--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Semith Kiliçsoy</t>
+          <t>Semih Kılıçsoy</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Samu Aghehowa</t>
+          <t>Samu Omorodion</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>K. Kvaratskhelia</t>
+          <t>Khvicha Kvaratskhelia</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>C. Summerville</t>
+          <t>Crysencio Summerville</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Kenan Yildiz</t>
+          <t>Kenan Yıldız</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Baris Alper Yılmaz</t>
+          <t>Barış Alper Yılmaz</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Ferdi Kadioğlu</t>
+          <t>Ferdi Kadıoğlu</t>
         </is>
       </c>
       <c r="C146" s="3" t="n"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Jakud Kiwior</t>
+          <t>Jakub Kiwior</t>
         </is>
       </c>
       <c r="C154" s="3" t="n"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>T. Alexander-Arnold</t>
+          <t>Trent Alexander-Arnold</t>
         </is>
       </c>
       <c r="C158" s="3" t="n"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Alex Zendejas</t>
+          <t>Alejandro Zendejas</t>
         </is>
       </c>
       <c r="C161" s="3" t="n"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Bruno Fernandez</t>
+          <t>Bruno Fernandes</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Semith Kiliçsoy</t>
+          <t>Semih Kılıçsoy</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Kenan Yildiz</t>
+          <t>Kenan Yıldız</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>C. Summerville</t>
+          <t>Crysencio Summerville</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>K. Kvaratskhelia</t>
+          <t>Khvicha Kvaratskhelia</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Alex Zendejas</t>
+          <t>Alejandro Zendejas</t>
         </is>
       </c>
       <c r="C81" s="3" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Arda Güler (P)</t>
+          <t>Arda Güler</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BC49AD-A3A8-4AF6-9A68-49EE84D8A007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3ECC05F-7E4A-4F29-ADB7-1AC8D9141D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$244</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
@@ -82,12 +82,25 @@
     <definedName name="Wrexham" localSheetId="5">BD!$P$2:$P$24</definedName>
     <definedName name="WREXHAM">Lista!$R$2:$R$1048576</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -6910,13 +6923,13 @@
           <x14:formula1>
             <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A193, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B193:B258</xm:sqref>
+          <xm:sqref>B193:B226 B228:B258 B227</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{615D4765-D08C-4B4D-8747-FBF8EC6F5D94}">
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A193:A258</xm:sqref>
+          <xm:sqref>A193:A226 A228:A258 A227</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8812,8 +8825,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -8836,7 +8848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -8844,11 +8856,11 @@
         <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -8862,7 +8874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -8876,7 +8888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -8888,7 +8900,7 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -8902,7 +8914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -8916,7 +8928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
@@ -8930,7 +8942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -8944,7 +8956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>44</v>
       </c>
@@ -8958,7 +8970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -8970,7 +8982,7 @@
       </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
@@ -8984,7 +8996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
@@ -8996,7 +9008,7 @@
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -9008,7 +9020,7 @@
       </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -9022,7 +9034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>42</v>
       </c>
@@ -9034,7 +9046,7 @@
       </c>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
@@ -9048,7 +9060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -9062,7 +9074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>44</v>
       </c>
@@ -9076,7 +9088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>44</v>
       </c>
@@ -9090,7 +9102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
@@ -9104,7 +9116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -9118,7 +9130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
@@ -9132,7 +9144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -9146,7 +9158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -9158,7 +9170,7 @@
       </c>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -9170,7 +9182,7 @@
       </c>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
@@ -9182,7 +9194,7 @@
       </c>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>20</v>
       </c>
@@ -9194,7 +9206,7 @@
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -9206,7 +9218,7 @@
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
@@ -9218,7 +9230,7 @@
       </c>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -9232,7 +9244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
@@ -9246,7 +9258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>49</v>
       </c>
@@ -9258,7 +9270,7 @@
       </c>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>26</v>
       </c>
@@ -9270,7 +9282,7 @@
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>26</v>
       </c>
@@ -9284,7 +9296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>55</v>
       </c>
@@ -9292,11 +9304,11 @@
         <v>242</v>
       </c>
       <c r="C36" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>20</v>
       </c>
@@ -9308,7 +9320,7 @@
       </c>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>119</v>
       </c>
@@ -9320,7 +9332,7 @@
       </c>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>119</v>
       </c>
@@ -9334,7 +9346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>20</v>
       </c>
@@ -9344,9 +9356,11 @@
       <c r="C40" s="3">
         <v>1</v>
       </c>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>17</v>
       </c>
@@ -9360,7 +9374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>36</v>
       </c>
@@ -9374,7 +9388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>36</v>
       </c>
@@ -9388,7 +9402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
@@ -9400,7 +9414,7 @@
       </c>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
@@ -9414,7 +9428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>4</v>
       </c>
@@ -9428,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>4</v>
       </c>
@@ -9442,7 +9456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>32</v>
       </c>
@@ -9454,7 +9468,7 @@
       </c>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>17</v>
       </c>
@@ -9468,7 +9482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>44</v>
       </c>
@@ -9480,7 +9494,7 @@
       </c>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>44</v>
       </c>
@@ -9492,7 +9506,7 @@
       </c>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>7</v>
       </c>
@@ -9504,7 +9518,7 @@
       </c>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>7</v>
       </c>
@@ -9518,7 +9532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>32</v>
       </c>
@@ -9530,7 +9544,7 @@
       </c>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
@@ -9544,7 +9558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>40</v>
       </c>
@@ -9556,7 +9570,7 @@
       </c>
       <c r="D56" s="3"/>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -9568,7 +9582,7 @@
       </c>
       <c r="D57" s="3"/>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>44</v>
       </c>
@@ -9580,7 +9594,7 @@
       </c>
       <c r="D58" s="3"/>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>7</v>
       </c>
@@ -9592,7 +9606,7 @@
       </c>
       <c r="D59" s="3"/>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>4</v>
       </c>
@@ -9604,7 +9618,7 @@
       </c>
       <c r="D60" s="3"/>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>55</v>
       </c>
@@ -9618,7 +9632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>55</v>
       </c>
@@ -9626,11 +9640,11 @@
         <v>78</v>
       </c>
       <c r="C62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>119</v>
       </c>
@@ -9644,7 +9658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>42</v>
       </c>
@@ -9656,7 +9670,7 @@
       </c>
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>42</v>
       </c>
@@ -9668,7 +9682,7 @@
       </c>
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>17</v>
       </c>
@@ -9680,7 +9694,7 @@
       </c>
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>32</v>
       </c>
@@ -9692,7 +9706,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>4</v>
       </c>
@@ -9704,7 +9718,7 @@
       </c>
       <c r="D68" s="3"/>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>38</v>
       </c>
@@ -9716,7 +9730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>49</v>
       </c>
@@ -9728,7 +9742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>26</v>
       </c>
@@ -9740,7 +9754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
@@ -9752,7 +9766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
@@ -9764,7 +9778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>32</v>
       </c>
@@ -9776,7 +9790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>4</v>
       </c>
@@ -9788,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>36</v>
       </c>
@@ -9800,7 +9814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>7</v>
       </c>
@@ -9812,7 +9826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>55</v>
       </c>
@@ -9824,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>40</v>
       </c>
@@ -9836,7 +9850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>17</v>
       </c>
@@ -9848,7 +9862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>42</v>
       </c>
@@ -9860,7 +9874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>49</v>
       </c>
@@ -9872,7 +9886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>40</v>
       </c>
@@ -9884,7 +9898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>40</v>
       </c>
@@ -9896,7 +9910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>4</v>
       </c>
@@ -9908,7 +9922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>7</v>
       </c>
@@ -9920,7 +9934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>4</v>
       </c>
@@ -9932,7 +9946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>55</v>
       </c>
@@ -9940,13 +9954,13 @@
         <v>57</v>
       </c>
       <c r="C88" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>26</v>
       </c>
@@ -9954,13 +9968,13 @@
         <v>89</v>
       </c>
       <c r="C89" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>20</v>
       </c>
@@ -9972,7 +9986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>20</v>
       </c>
@@ -9981,10 +9995,10 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>42</v>
       </c>
@@ -9996,7 +10010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>44</v>
       </c>
@@ -10008,7 +10022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>42</v>
       </c>
@@ -10020,7 +10034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>36</v>
       </c>
@@ -10032,7 +10046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>32</v>
       </c>
@@ -10044,7 +10058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>7</v>
       </c>
@@ -10056,7 +10070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>38</v>
       </c>
@@ -10068,7 +10082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>26</v>
       </c>
@@ -10080,7 +10094,7 @@
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>26</v>
       </c>
@@ -10094,7 +10108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>26</v>
       </c>
@@ -10102,13 +10116,13 @@
         <v>29</v>
       </c>
       <c r="C101" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>55</v>
       </c>
@@ -10122,7 +10136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>55</v>
       </c>
@@ -10134,7 +10148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>49</v>
       </c>
@@ -10182,7 +10196,7 @@
       </c>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>26</v>
       </c>
@@ -10193,10 +10207,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>49</v>
       </c>
@@ -10208,7 +10222,7 @@
       </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>55</v>
       </c>
@@ -10247,51 +10261,99 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
+      <c r="A113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C113" s="3">
+        <v>1</v>
+      </c>
       <c r="D113" s="3"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
+      <c r="A114" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="A115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1</v>
+      </c>
       <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="A116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="3">
+        <v>2</v>
+      </c>
       <c r="D116" s="3"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
+      <c r="A117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
+      <c r="D117" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
+      <c r="A118" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
       <c r="D118" s="3"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
+      <c r="A119" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
+      <c r="D119" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
+      <c r="A120" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
       <c r="D120" s="3"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -11068,24 +11130,31 @@
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="3"/>
-      <c r="B250" s="3"/>
-      <c r="C250" s="3"/>
-      <c r="D250" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D112" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Borussia_Dortmund"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:D120" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D97">
       <sortCondition descending="1" ref="C1:C96"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E250D98B-9CCC-416D-AE1D-D017ADBFE043}">
+          <x14:formula1>
+            <xm:f>BD!$A$1:$Q$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>A113:A249</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80734617-1728-4B7E-B0AF-D27C7785F7A5}">
+          <x14:formula1>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A113, BD!$A$1:$Q$1, 0))</xm:f>
+          </x14:formula1>
+          <xm:sqref>B113:B249</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3ECC05F-7E4A-4F29-ADB7-1AC8D9141D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7ADFEE-962B-46DB-9CB5-9B3FAAF67982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$244</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$43</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -11144,13 +11144,13 @@
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A113:A249</xm:sqref>
+          <xm:sqref>A113:A120 A122:A249 A121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80734617-1728-4B7E-B0AF-D27C7785F7A5}">
           <x14:formula1>
             <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A113, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B113:B249</xm:sqref>
+          <xm:sqref>B113:B120 B122:B249 B121</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11377,7 +11377,9 @@
       <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
@@ -11508,141 +11510,291 @@
       <c r="D27" s="6"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
       <c r="D28" s="6"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="A29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6">
+        <v>3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="D30" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+      <c r="A31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
       <c r="D31" s="6"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="A32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="A33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
+      <c r="A34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="A35" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="6">
+        <v>4</v>
+      </c>
+      <c r="D35" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="A36" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
+      <c r="A37" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3</v>
+      </c>
       <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
+      <c r="A38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
       <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
+      <c r="A39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="D40" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+      <c r="A41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
       <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
+      <c r="A42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>283</v>
+      </c>
       <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>448</v>
+      </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="D43" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
+      <c r="A44" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
+      <c r="A45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1</v>
+      </c>
       <c r="D45" s="6"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C46" s="6">
+        <v>2</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="D47" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
       <c r="D48" s="6"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="D49" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
+      <c r="A50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
       <c r="D50" s="6"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -12846,12 +12998,30 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000004000000}">
+  <autoFilter ref="A1:D43" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
       <sortCondition descending="1" ref="D1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{374493D9-AC47-4788-9F41-439855E9DEA9}">
+          <x14:formula1>
+            <xm:f>BD!$A$1:$Q$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>A28:A250</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFD4B24B-070B-4416-AB24-2DA5DDD7D826}">
+          <x14:formula1>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A28, BD!$A$1:$Q$1, 0))</xm:f>
+          </x14:formula1>
+          <xm:sqref>B28:B250</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7ADFEE-962B-46DB-9CB5-9B3FAAF67982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37ECC690-4FF4-4C09-BD6A-9D42E252499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$244</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$50</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -11185,237 +11185,245 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="6">
         <v>5</v>
       </c>
-      <c r="C2" s="6">
-        <v>1</v>
-      </c>
       <c r="D2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="6">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6"/>
       <c r="D3" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C4" s="6">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2</v>
+      </c>
       <c r="D7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="C9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="6"/>
+        <v>494</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
       <c r="D12" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
         <v>2</v>
       </c>
-      <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -11423,14 +11431,16 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
       <c r="D21" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -11452,33 +11462,33 @@
         <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
       <c r="D23" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="6">
         <v>1</v>
@@ -11487,34 +11497,36 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
@@ -11526,59 +11538,57 @@
         <v>51</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>52</v>
+        <v>318</v>
       </c>
       <c r="C29" s="6">
-        <v>3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="6"/>
+        <v>131</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
       <c r="D30" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="C31" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="6"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C32" s="6">
         <v>1</v>
       </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="C33" s="6">
         <v>1</v>
@@ -11587,10 +11597,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>318</v>
+        <v>108</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -11599,74 +11609,72 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C35" s="6">
-        <v>4</v>
-      </c>
-      <c r="D35" s="6">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
       </c>
-      <c r="D36" s="6">
-        <v>1</v>
-      </c>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C37" s="6">
-        <v>3</v>
-      </c>
-      <c r="D37" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="C38" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6">
@@ -11675,22 +11683,22 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1</v>
-      </c>
-      <c r="D41" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>283</v>
+        <v>11</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6">
@@ -11699,10 +11707,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>448</v>
+        <v>14</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6">
@@ -11711,50 +11719,46 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="C44" s="6">
-        <v>2</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1</v>
-      </c>
-      <c r="D45" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="C46" s="6">
-        <v>2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C46" s="6"/>
       <c r="D46" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6">
@@ -11763,22 +11767,22 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="6">
-        <v>1</v>
-      </c>
-      <c r="D48" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>339</v>
+        <v>30</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6">
@@ -11787,81 +11791,147 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="6">
-        <v>1</v>
-      </c>
-      <c r="D50" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+      <c r="D51" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
+      <c r="D52" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="D53" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
+      <c r="A54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>283</v>
+      </c>
       <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>448</v>
+      </c>
       <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
+      <c r="D55" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
+      <c r="D56" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>213</v>
+      </c>
       <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
+      <c r="D58" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>491</v>
+      </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
+      <c r="D59" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>258</v>
+      </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="D60" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="D61" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
@@ -12998,9 +13068,9 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
-      <sortCondition descending="1" ref="D1"/>
+  <autoFilter ref="A1:D50" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
+      <sortCondition descending="1" ref="C1:C50"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37ECC690-4FF4-4C09-BD6A-9D42E252499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF457E43-353C-4D80-990C-02255B6E2713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$50</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3781,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3812,10 +3812,10 @@
         <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3840,7 +3840,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
@@ -3848,27 +3848,27 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -3876,38 +3876,38 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3">
         <v>11</v>
       </c>
       <c r="D8" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3">
         <v>11</v>
@@ -3918,16 +3918,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C10" s="3">
         <v>11</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -3952,7 +3952,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -3960,13 +3960,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -3980,10 +3980,10 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -3991,7 +3991,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3">
         <v>8</v>
@@ -4002,13 +4002,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -4016,38 +4016,38 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="C18" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3">
         <v>7</v>
@@ -4058,30 +4058,30 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C20" s="3">
         <v>7</v>
       </c>
       <c r="D20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4089,10 +4089,10 @@
         <v>55</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -4100,44 +4100,44 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
         <v>6</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4145,75 +4145,75 @@
         <v>55</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3">
-        <v>6</v>
-      </c>
-      <c r="D26" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3">
         <v>6</v>
       </c>
       <c r="D27" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C28" s="3">
         <v>6</v>
       </c>
       <c r="D28" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C29" s="3">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3">
         <v>5</v>
       </c>
       <c r="D30" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3">
         <v>5</v>
@@ -4261,7 +4261,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -4286,7 +4286,7 @@
         <v>66</v>
       </c>
       <c r="C36" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
@@ -4294,58 +4294,58 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C38" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C40" s="3">
         <v>4</v>
       </c>
       <c r="D40" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -4353,122 +4353,122 @@
         <v>44</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C41" s="3">
         <v>4</v>
       </c>
       <c r="D41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C42" s="3">
         <v>4</v>
       </c>
       <c r="D42" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C43" s="3">
         <v>4</v>
       </c>
       <c r="D43" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C44" s="3">
         <v>4</v>
       </c>
       <c r="D44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C45" s="3">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
         <v>3</v>
-      </c>
-      <c r="D45" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="C46" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="C47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="C48" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="C49" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -4479,47 +4479,49 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C50" s="3">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3">
         <v>3</v>
       </c>
-      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="C51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C52" s="3">
         <v>3</v>
       </c>
       <c r="D52" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C53" s="3">
         <v>3</v>
@@ -4530,133 +4532,133 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="C54" s="3">
         <v>3</v>
       </c>
       <c r="D54" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="C55" s="3">
         <v>3</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>208</v>
+        <v>5</v>
       </c>
       <c r="C56" s="3">
         <v>3</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
       </c>
-      <c r="D57" s="3">
-        <v>2</v>
-      </c>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="C58" s="3">
         <v>3</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3">
+        <v>14</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="C59" s="3">
         <v>3</v>
       </c>
       <c r="D59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>353</v>
+        <v>121</v>
       </c>
       <c r="C60" s="3">
         <v>3</v>
       </c>
       <c r="D60" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="C61" s="3">
-        <v>2</v>
-      </c>
-      <c r="D61" s="3">
-        <v>8</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
-      </c>
-      <c r="D62" s="3">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="C63" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -4667,66 +4669,64 @@
         <v>36</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C65" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C66" s="3">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3">
         <v>2</v>
-      </c>
-      <c r="D66" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="C67" s="3">
-        <v>2</v>
-      </c>
-      <c r="D67" s="3">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="C68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -4734,27 +4734,27 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="C69" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="C70" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -4762,13 +4762,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="C71" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -4776,128 +4776,136 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="C72" s="3">
         <v>2</v>
       </c>
       <c r="D72" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C73" s="3">
         <v>2</v>
       </c>
       <c r="D73" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C74" s="3">
         <v>2</v>
       </c>
       <c r="D74" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C75" s="3">
         <v>2</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C76" s="3">
         <v>2</v>
       </c>
-      <c r="D76" s="3"/>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C77" s="3">
         <v>2</v>
       </c>
-      <c r="D77" s="3"/>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C78" s="3">
         <v>2</v>
       </c>
-      <c r="D78" s="3"/>
+      <c r="D78" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="C79" s="3">
         <v>2</v>
       </c>
       <c r="D79" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C80" s="3">
         <v>2</v>
       </c>
       <c r="D80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="C81" s="3">
         <v>2</v>
@@ -4908,38 +4916,36 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C82" s="3">
         <v>2</v>
       </c>
       <c r="D82" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C83" s="3">
         <v>2</v>
       </c>
-      <c r="D83" s="3">
-        <v>1</v>
-      </c>
+      <c r="D83" s="3"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4948,10 +4954,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C85" s="3">
         <v>2</v>
@@ -4960,10 +4966,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
@@ -4972,38 +4978,38 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="C87" s="3">
         <v>2</v>
       </c>
       <c r="D87" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
       </c>
       <c r="D88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="C89" s="3">
         <v>2</v>
@@ -5014,10 +5020,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
@@ -5029,118 +5035,116 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C91" s="3">
         <v>2</v>
       </c>
-      <c r="D91" s="3">
-        <v>1</v>
-      </c>
+      <c r="D91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
-      <c r="D92" s="3"/>
+      <c r="D92" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C93" s="3">
         <v>2</v>
       </c>
       <c r="D93" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
       </c>
-      <c r="D94" s="3"/>
+      <c r="D94" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C95" s="3">
         <v>2</v>
       </c>
-      <c r="D95" s="3">
-        <v>1</v>
-      </c>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>11</v>
+        <v>197</v>
       </c>
       <c r="C96" s="3">
         <v>2</v>
       </c>
       <c r="D96" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C97" s="3">
         <v>2</v>
       </c>
-      <c r="D97" s="3">
-        <v>1</v>
-      </c>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="C98" s="3">
         <v>2</v>
       </c>
       <c r="D98" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
@@ -5149,10 +5153,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>448</v>
+        <v>147</v>
       </c>
       <c r="C100" s="3">
         <v>2</v>
@@ -5161,288 +5165,296 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>142</v>
+        <v>448</v>
       </c>
       <c r="C101" s="3">
         <v>2</v>
       </c>
-      <c r="D101" s="3">
-        <v>2</v>
-      </c>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="C102" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103" s="3">
-        <v>1</v>
-      </c>
-      <c r="D103" s="3">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>9</v>
+        <v>196</v>
       </c>
       <c r="C104" s="3">
-        <v>1</v>
-      </c>
-      <c r="D104" s="3">
         <v>2</v>
       </c>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="C105" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C106" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="C107" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="C108" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C109" s="3">
-        <v>1</v>
-      </c>
-      <c r="D109" s="3">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="C110" s="3">
         <v>1</v>
       </c>
       <c r="D110" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C111" s="3">
         <v>1</v>
       </c>
       <c r="D111" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="C112" s="3">
         <v>1</v>
       </c>
       <c r="D112" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C113" s="3">
         <v>1</v>
       </c>
       <c r="D113" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C114" s="3">
         <v>1</v>
       </c>
-      <c r="D114" s="3"/>
+      <c r="D114" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C115" s="3">
         <v>1</v>
       </c>
-      <c r="D115" s="3"/>
+      <c r="D115" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C116" s="3">
         <v>1</v>
       </c>
-      <c r="D116" s="3"/>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C117" s="3">
         <v>1</v>
       </c>
-      <c r="D117" s="3"/>
+      <c r="D117" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C118" s="3">
         <v>1</v>
       </c>
-      <c r="D118" s="3"/>
+      <c r="D118" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C119" s="3">
         <v>1</v>
       </c>
-      <c r="D119" s="3"/>
+      <c r="D119" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C120" s="3">
         <v>1</v>
       </c>
-      <c r="D120" s="3"/>
+      <c r="D120" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C121" s="3">
         <v>1</v>
       </c>
-      <c r="D121" s="3"/>
+      <c r="D121" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C122" s="3">
         <v>1</v>
@@ -5451,10 +5463,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C123" s="3">
         <v>1</v>
@@ -5463,10 +5475,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C124" s="3">
         <v>1</v>
@@ -5475,10 +5487,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C125" s="3">
         <v>1</v>
@@ -5487,10 +5499,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="C126" s="3">
         <v>1</v>
@@ -5499,24 +5511,22 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C127" s="3">
         <v>1</v>
       </c>
-      <c r="D127" s="3">
-        <v>1</v>
-      </c>
+      <c r="D127" s="3"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C128" s="3">
         <v>1</v>
@@ -5525,10 +5535,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C129" s="3">
         <v>1</v>
@@ -5537,10 +5547,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C130" s="3">
         <v>1</v>
@@ -5549,10 +5559,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="C131" s="3">
         <v>1</v>
@@ -5561,10 +5571,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C132" s="3">
         <v>1</v>
@@ -5573,10 +5583,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C133" s="3">
         <v>1</v>
@@ -5585,22 +5595,24 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C134" s="3">
         <v>1</v>
       </c>
-      <c r="D134" s="3"/>
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C135" s="3">
         <v>1</v>
@@ -5609,10 +5621,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C136" s="3">
         <v>1</v>
@@ -5621,10 +5633,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C137" s="3">
         <v>1</v>
@@ -5633,10 +5645,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="C138" s="3">
         <v>1</v>
@@ -5645,10 +5657,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C139" s="3">
         <v>1</v>
@@ -5657,10 +5669,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C140" s="3">
         <v>1</v>
@@ -5669,10 +5681,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C141" s="3">
         <v>1</v>
@@ -5681,38 +5693,34 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
       </c>
-      <c r="D142" s="3">
-        <v>1</v>
-      </c>
+      <c r="D142" s="3"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="C143" s="3">
         <v>1</v>
       </c>
-      <c r="D143" s="3">
-        <v>1</v>
-      </c>
+      <c r="D143" s="3"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>193</v>
+        <v>7</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
@@ -5721,24 +5729,22 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="C145" s="3">
         <v>1</v>
       </c>
-      <c r="D145" s="3">
-        <v>1</v>
-      </c>
+      <c r="D145" s="3"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="C146" s="3">
         <v>1</v>
@@ -5747,10 +5753,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="C147" s="3">
         <v>1</v>
@@ -5759,10 +5765,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C148" s="3">
         <v>1</v>
@@ -5771,10 +5777,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="C149" s="3">
         <v>1</v>
@@ -5785,10 +5791,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>362</v>
+        <v>198</v>
       </c>
       <c r="C150" s="3">
         <v>1</v>
@@ -5799,38 +5805,34 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="C151" s="3">
         <v>1</v>
       </c>
-      <c r="D151" s="3">
-        <v>3</v>
-      </c>
+      <c r="D151" s="3"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>355</v>
+        <v>210</v>
       </c>
       <c r="C152" s="3">
         <v>1</v>
       </c>
-      <c r="D152" s="3">
-        <v>1</v>
-      </c>
+      <c r="D152" s="3"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="C153" s="3">
         <v>1</v>
@@ -5839,74 +5841,78 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
       </c>
-      <c r="D154" s="3"/>
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
-      <c r="D155" s="3"/>
+      <c r="D155" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
       </c>
-      <c r="D156" s="3"/>
+      <c r="D156" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>464</v>
+        <v>355</v>
       </c>
       <c r="C157" s="3">
         <v>1</v>
       </c>
       <c r="D157" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C158" s="3">
         <v>1</v>
       </c>
-      <c r="D158" s="3">
-        <v>1</v>
-      </c>
+      <c r="D158" s="3"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>488</v>
+        <v>251</v>
       </c>
       <c r="C159" s="3">
         <v>1</v>
@@ -5915,10 +5921,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>456</v>
+        <v>492</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
@@ -5927,10 +5933,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>474</v>
+        <v>316</v>
       </c>
       <c r="C161" s="3">
         <v>1</v>
@@ -5939,142 +5945,146 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C162" s="3"/>
+        <v>464</v>
+      </c>
+      <c r="C162" s="3">
+        <v>1</v>
+      </c>
       <c r="D162" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3">
-        <v>4</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C163" s="3">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3">
-        <v>3</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C164" s="3">
+        <v>1</v>
+      </c>
+      <c r="D164" s="3"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3">
-        <v>3</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C165" s="3">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C166" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="C166" s="3">
+        <v>1</v>
+      </c>
       <c r="D166" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3">
-        <v>2</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="C167" s="3">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3">
-        <v>3</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C168" s="3">
+        <v>1</v>
+      </c>
+      <c r="D168" s="3"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3">
-        <v>2</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C169" s="3">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3">
-        <v>2</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="C170" s="3">
+        <v>1</v>
+      </c>
+      <c r="D170" s="3"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3">
@@ -6083,34 +6093,34 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3">
@@ -6119,10 +6129,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3">
@@ -6131,94 +6141,94 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3">
@@ -6227,10 +6237,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3">
@@ -6239,22 +6249,22 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3">
@@ -6263,10 +6273,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6278,7 +6288,7 @@
         <v>17</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3">
@@ -6287,46 +6297,46 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3">
@@ -6335,10 +6345,10 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3">
@@ -6347,10 +6357,10 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3">
@@ -6359,14 +6369,14 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -6374,7 +6384,7 @@
         <v>42</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3">
@@ -6383,10 +6393,10 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3">
@@ -6395,10 +6405,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3">
@@ -6407,10 +6417,10 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3">
@@ -6419,10 +6429,10 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3">
@@ -6434,7 +6444,7 @@
         <v>17</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3">
@@ -6443,10 +6453,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3">
@@ -6455,10 +6465,10 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3">
@@ -6467,10 +6477,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3">
@@ -6479,10 +6489,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3">
@@ -6491,10 +6501,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3">
@@ -6503,10 +6513,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3">
@@ -6515,10 +6525,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3">
@@ -6527,58 +6537,58 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>409</v>
+        <v>201</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3">
@@ -6587,10 +6597,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>436</v>
+        <v>209</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3">
@@ -6599,58 +6609,58 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>329</v>
+        <v>212</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>128</v>
+        <v>409</v>
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>278</v>
+        <v>182</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>371</v>
+        <v>12</v>
       </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>6</v>
+        <v>436</v>
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3">
@@ -6659,22 +6669,22 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>431</v>
+        <v>128</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3">
@@ -6683,34 +6693,34 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>321</v>
+        <v>6</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3">
@@ -6718,82 +6728,160 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="3"/>
-      <c r="B227" s="3"/>
+      <c r="A227" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="C227" s="3"/>
-      <c r="D227" s="3"/>
+      <c r="D227" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="3"/>
-      <c r="B228" s="3"/>
+      <c r="A228" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="C228" s="3"/>
-      <c r="D228" s="3"/>
+      <c r="D228" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
+      <c r="A229" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="C229" s="3"/>
-      <c r="D229" s="3"/>
+      <c r="D229" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="3"/>
-      <c r="B230" s="3"/>
+      <c r="A230" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="C230" s="3"/>
-      <c r="D230" s="3"/>
+      <c r="D230" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
+      <c r="A231" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="C231" s="3"/>
-      <c r="D231" s="3"/>
+      <c r="D231" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="3"/>
-      <c r="B232" s="3"/>
+      <c r="A232" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="C232" s="3"/>
-      <c r="D232" s="3"/>
+      <c r="D232" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="3"/>
-      <c r="B233" s="3"/>
+      <c r="A233" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="C233" s="3"/>
-      <c r="D233" s="3"/>
+      <c r="D233" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3"/>
+      <c r="A234" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="C234" s="3"/>
-      <c r="D234" s="3"/>
+      <c r="D234" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" s="3"/>
-      <c r="B235" s="3"/>
+      <c r="A235" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="C235" s="3"/>
-      <c r="D235" s="3"/>
+      <c r="D235" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3"/>
+      <c r="A236" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>469</v>
+      </c>
       <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
+      <c r="D236" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="3"/>
-      <c r="B237" s="3"/>
+      <c r="A237" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="C237" s="3"/>
-      <c r="D237" s="3"/>
+      <c r="D237" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="3"/>
-      <c r="B238" s="3"/>
+      <c r="A238" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
+      <c r="D238" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="3"/>
-      <c r="B239" s="3"/>
+      <c r="A239" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>440</v>
+      </c>
       <c r="C239" s="3"/>
-      <c r="D239" s="3"/>
+      <c r="D239" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
@@ -6903,16 +6991,10 @@
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258" s="3"/>
-      <c r="B258" s="3"/>
-      <c r="C258" s="3"/>
-      <c r="D258" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D244" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D244">
-      <sortCondition descending="1" ref="C1:C244"/>
+  <autoFilter ref="A1:D243" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D243">
+      <sortCondition descending="1" ref="C1:C243"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6923,13 +7005,13 @@
           <x14:formula1>
             <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A193, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B193:B226 B228:B258 B227</xm:sqref>
+          <xm:sqref>B193:B257</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{615D4765-D08C-4B4D-8747-FBF8EC6F5D94}">
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A193:A226 A228:A258 A227</xm:sqref>
+          <xm:sqref>A193:A257</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF457E43-353C-4D80-990C-02255B6E2713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895DCCD6-C855-4B93-979C-2745ECD01F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4258,7 +4258,7 @@
         <v>214</v>
       </c>
       <c r="C34" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" s="3">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         <v>194</v>
       </c>
       <c r="C95" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" s="3"/>
     </row>
@@ -5107,7 +5107,7 @@
         <v>197</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" s="3">
         <v>2</v>
@@ -5211,7 +5211,9 @@
       <c r="C104" s="3">
         <v>2</v>
       </c>
-      <c r="D104" s="3"/>
+      <c r="D104" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
@@ -5266,7 +5268,7 @@
         <v>2</v>
       </c>
       <c r="D108" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -5835,7 +5837,7 @@
         <v>213</v>
       </c>
       <c r="C153" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" s="3"/>
     </row>
@@ -6868,7 +6870,7 @@
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895DCCD6-C855-4B93-979C-2745ECD01F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC371E4-263E-419C-88EE-0C98FB406B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$243</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$64</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3854,10 +3854,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4036,7 +4036,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>7</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4120,7 +4120,7 @@
         <v>13</v>
       </c>
       <c r="C24" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
         <v>5</v>
@@ -4134,7 +4134,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>107</v>
       </c>
       <c r="C37" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
@@ -4429,7 +4429,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -4810,10 +4810,10 @@
         <v>87</v>
       </c>
       <c r="C74" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -4852,7 +4852,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         <v>2</v>
       </c>
       <c r="D93" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -5095,7 +5095,7 @@
         <v>194</v>
       </c>
       <c r="C95" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" s="3"/>
     </row>
@@ -5107,10 +5107,10 @@
         <v>197</v>
       </c>
       <c r="C96" s="3">
+        <v>4</v>
+      </c>
+      <c r="D96" s="3">
         <v>3</v>
-      </c>
-      <c r="D96" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -5209,10 +5209,10 @@
         <v>196</v>
       </c>
       <c r="C104" s="3">
+        <v>3</v>
+      </c>
+      <c r="D104" s="3">
         <v>2</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -5364,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -5406,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -5799,7 +5799,7 @@
         <v>198</v>
       </c>
       <c r="C150" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="3">
         <v>1</v>
@@ -5837,7 +5837,7 @@
         <v>213</v>
       </c>
       <c r="C153" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" s="3"/>
     </row>
@@ -5863,7 +5863,7 @@
         <v>362</v>
       </c>
       <c r="C155" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" s="3">
         <v>1</v>
@@ -6148,7 +6148,9 @@
       <c r="B178" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C178" s="3"/>
+      <c r="C178" s="3">
+        <v>1</v>
+      </c>
       <c r="D178" s="3">
         <v>3</v>
       </c>
@@ -6210,7 +6212,7 @@
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -6606,7 +6608,7 @@
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -6628,7 +6630,9 @@
       <c r="B218" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C218" s="3"/>
+      <c r="C218" s="3">
+        <v>1</v>
+      </c>
       <c r="D218" s="3">
         <v>5</v>
       </c>
@@ -6886,28 +6890,52 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="3"/>
-      <c r="B240" s="3"/>
+      <c r="A240" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>443</v>
+      </c>
       <c r="C240" s="3"/>
-      <c r="D240" s="3"/>
+      <c r="D240" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="3"/>
-      <c r="B241" s="3"/>
+      <c r="A241" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="C241" s="3"/>
-      <c r="D241" s="3"/>
+      <c r="D241" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="3"/>
-      <c r="B242" s="3"/>
+      <c r="A242" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
+      <c r="D242" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="3"/>
-      <c r="B243" s="3"/>
+      <c r="A243" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="C243" s="3"/>
-      <c r="D243" s="3"/>
+      <c r="D243" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
@@ -12018,34 +12046,66 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
+      <c r="A62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1</v>
+      </c>
       <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="D63" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
+      <c r="A64" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="6">
+        <v>1</v>
+      </c>
       <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
+      <c r="A65" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
       <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="A66" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="6">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
@@ -13152,7 +13212,7 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D50" xr:uid="{00000000-0009-0000-0000-000004000000}">
+  <autoFilter ref="A1:D64" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
       <sortCondition descending="1" ref="C1:C50"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC371E4-263E-419C-88EE-0C98FB406B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1672231C-0032-41E4-B307-9F337A17F5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$248</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$64</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3812,7 +3812,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
         <v>8</v>
@@ -3820,16 +3820,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -3840,7 +3840,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
@@ -3848,16 +3848,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -3868,7 +3868,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -3932,24 +3932,24 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
         <v>10</v>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3">
         <v>10</v>
@@ -3974,30 +3974,30 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -4005,7 +4005,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3">
         <v>8</v>
@@ -4016,80 +4016,80 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3">
         <v>8</v>
       </c>
       <c r="D17" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3">
         <v>7</v>
       </c>
       <c r="D21" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3">
         <v>7</v>
@@ -4100,44 +4100,44 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="C23" s="3">
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="3">
         <v>7</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="3">
-        <v>8</v>
-      </c>
       <c r="D24" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4156,13 +4156,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="C27" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3">
         <v>2</v>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C28" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="3">
         <v>2</v>
@@ -4184,53 +4184,53 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C29" s="3">
         <v>6</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" s="3">
-        <v>5</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3">
         <v>2</v>
@@ -4238,27 +4238,27 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C33" s="3">
         <v>5</v>
       </c>
       <c r="D33" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="C34" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" s="3">
         <v>2</v>
@@ -4266,44 +4266,44 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="C35" s="3">
         <v>5</v>
       </c>
       <c r="D35" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C36" s="3">
         <v>5</v>
       </c>
       <c r="D36" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -4359,7 +4359,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -4504,134 +4504,134 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>72</v>
+        <v>216</v>
       </c>
       <c r="C52" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="C54" s="3">
-        <v>3</v>
-      </c>
-      <c r="D54" s="3">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="C55" s="3">
+        <v>4</v>
+      </c>
+      <c r="D55" s="3">
         <v>3</v>
-      </c>
-      <c r="D55" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C56" s="3">
         <v>3</v>
       </c>
       <c r="D56" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C58" s="3">
         <v>3</v>
       </c>
       <c r="D58" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="C59" s="3">
         <v>3</v>
       </c>
       <c r="D59" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="C60" s="3">
         <v>3</v>
       </c>
       <c r="D60" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="C61" s="3">
         <v>3</v>
@@ -4640,22 +4640,24 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="C62" s="3">
         <v>3</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3">
+        <v>14</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="C63" s="3">
         <v>3</v>
@@ -4666,78 +4668,76 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C64" s="3">
         <v>3</v>
       </c>
       <c r="D64" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="C65" s="3">
         <v>3</v>
       </c>
-      <c r="D65" s="3">
-        <v>3</v>
-      </c>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="C66" s="3">
         <v>3</v>
       </c>
-      <c r="D66" s="3">
-        <v>2</v>
-      </c>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="C67" s="3">
         <v>3</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
       </c>
       <c r="D68" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="C69" s="3">
         <v>3</v>
@@ -4748,83 +4748,81 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="C70" s="3">
         <v>3</v>
       </c>
       <c r="D70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="C71" s="3">
         <v>3</v>
       </c>
-      <c r="D71" s="3">
-        <v>1</v>
-      </c>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="C72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="C73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="C74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C75" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
@@ -4832,13 +4830,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C76" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
@@ -4846,10 +4844,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C77" s="3">
         <v>3</v>
@@ -4860,41 +4858,39 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="C78" s="3">
+        <v>3</v>
+      </c>
+      <c r="D78" s="3">
         <v>2</v>
-      </c>
-      <c r="D78" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>14</v>
+        <v>213</v>
       </c>
       <c r="C79" s="3">
-        <v>2</v>
-      </c>
-      <c r="D79" s="3">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D79" s="3"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>96</v>
+        <v>362</v>
       </c>
       <c r="C80" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -4902,13 +4898,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
       <c r="C81" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3">
         <v>1</v>
@@ -4916,86 +4912,94 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="C82" s="3">
         <v>2</v>
       </c>
       <c r="D82" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C83" s="3">
         <v>2</v>
       </c>
-      <c r="D83" s="3"/>
+      <c r="D83" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
       </c>
-      <c r="D84" s="3"/>
+      <c r="D84" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C85" s="3">
         <v>2</v>
       </c>
-      <c r="D85" s="3"/>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
       </c>
-      <c r="D86" s="3"/>
+      <c r="D86" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C87" s="3">
         <v>2</v>
       </c>
       <c r="D87" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -5006,24 +5010,22 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C89" s="3">
         <v>2</v>
       </c>
-      <c r="D89" s="3">
-        <v>1</v>
-      </c>
+      <c r="D89" s="3"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
@@ -5035,10 +5037,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="C91" s="3">
         <v>2</v>
@@ -5047,24 +5049,22 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
-      <c r="D92" s="3">
-        <v>9</v>
-      </c>
+      <c r="D92" s="3"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C93" s="3">
         <v>2</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
@@ -5089,36 +5089,36 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="C95" s="3">
-        <v>4</v>
-      </c>
-      <c r="D95" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D95" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="C96" s="3">
-        <v>4</v>
-      </c>
-      <c r="D96" s="3">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D96" s="3"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="C97" s="3">
         <v>2</v>
@@ -5127,48 +5127,52 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="C98" s="3">
         <v>2</v>
       </c>
       <c r="D98" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
       </c>
-      <c r="D99" s="3"/>
+      <c r="D99" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="C100" s="3">
         <v>2</v>
       </c>
-      <c r="D100" s="3"/>
+      <c r="D100" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>448</v>
+        <v>200</v>
       </c>
       <c r="C101" s="3">
         <v>2</v>
@@ -5177,10 +5181,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="C102" s="3">
         <v>2</v>
@@ -5191,10 +5195,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="C103" s="3">
         <v>2</v>
@@ -5203,109 +5207,105 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="C104" s="3">
-        <v>3</v>
-      </c>
-      <c r="D104" s="3">
         <v>2</v>
       </c>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>31</v>
+        <v>448</v>
       </c>
       <c r="C105" s="3">
         <v>2</v>
       </c>
-      <c r="D105" s="3">
-        <v>1</v>
-      </c>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C106" s="3">
         <v>2</v>
       </c>
       <c r="D106" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="C107" s="3">
         <v>2</v>
       </c>
-      <c r="D107" s="3">
-        <v>1</v>
-      </c>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="C108" s="3">
         <v>2</v>
       </c>
       <c r="D108" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="C109" s="3">
         <v>2</v>
       </c>
-      <c r="D109" s="3"/>
+      <c r="D109" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="C110" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="C111" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3">
         <v>4</v>
@@ -5313,94 +5313,92 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="C112" s="3">
-        <v>1</v>
-      </c>
-      <c r="D112" s="3">
         <v>2</v>
       </c>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="C113" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="C114" s="3">
         <v>1</v>
       </c>
       <c r="D114" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C115" s="3">
         <v>1</v>
       </c>
       <c r="D115" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C116" s="3">
         <v>1</v>
       </c>
       <c r="D116" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C117" s="3">
         <v>1</v>
       </c>
       <c r="D117" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C118" s="3">
         <v>1</v>
@@ -5411,38 +5409,38 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C119" s="3">
         <v>1</v>
       </c>
       <c r="D119" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C120" s="3">
         <v>1</v>
       </c>
       <c r="D120" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C121" s="3">
         <v>1</v>
@@ -5453,58 +5451,66 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C122" s="3">
         <v>1</v>
       </c>
-      <c r="D122" s="3"/>
+      <c r="D122" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C123" s="3">
         <v>1</v>
       </c>
-      <c r="D123" s="3"/>
+      <c r="D123" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C124" s="3">
         <v>1</v>
       </c>
-      <c r="D124" s="3"/>
+      <c r="D124" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C125" s="3">
         <v>1</v>
       </c>
-      <c r="D125" s="3"/>
+      <c r="D125" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="C126" s="3">
         <v>1</v>
@@ -5513,10 +5519,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C127" s="3">
         <v>1</v>
@@ -5525,10 +5531,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C128" s="3">
         <v>1</v>
@@ -5537,10 +5543,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C129" s="3">
         <v>1</v>
@@ -5549,10 +5555,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="C130" s="3">
         <v>1</v>
@@ -5561,10 +5567,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C131" s="3">
         <v>1</v>
@@ -5573,10 +5579,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C132" s="3">
         <v>1</v>
@@ -5585,10 +5591,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C133" s="3">
         <v>1</v>
@@ -5597,24 +5603,22 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C134" s="3">
         <v>1</v>
       </c>
-      <c r="D134" s="3">
-        <v>1</v>
-      </c>
+      <c r="D134" s="3"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C135" s="3">
         <v>1</v>
@@ -5623,10 +5627,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C136" s="3">
         <v>1</v>
@@ -5635,10 +5639,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C137" s="3">
         <v>1</v>
@@ -5650,19 +5654,21 @@
         <v>26</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="C138" s="3">
         <v>1</v>
       </c>
-      <c r="D138" s="3"/>
+      <c r="D138" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C139" s="3">
         <v>1</v>
@@ -5671,10 +5677,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C140" s="3">
         <v>1</v>
@@ -5683,10 +5689,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C141" s="3">
         <v>1</v>
@@ -5695,10 +5701,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
@@ -5707,10 +5713,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C143" s="3">
         <v>1</v>
@@ -5719,10 +5725,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
@@ -5731,10 +5737,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="C145" s="3">
         <v>1</v>
@@ -5743,10 +5749,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C146" s="3">
         <v>1</v>
@@ -5758,7 +5764,7 @@
         <v>32</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C147" s="3">
         <v>1</v>
@@ -5767,10 +5773,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C148" s="3">
         <v>1</v>
@@ -5779,38 +5785,34 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C149" s="3">
         <v>1</v>
       </c>
-      <c r="D149" s="3">
-        <v>1</v>
-      </c>
+      <c r="D149" s="3"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="C150" s="3">
-        <v>2</v>
-      </c>
-      <c r="D150" s="3">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D150" s="3"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="C151" s="3">
         <v>1</v>
@@ -5819,10 +5821,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="C152" s="3">
         <v>1</v>
@@ -5831,90 +5833,90 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="C153" s="3">
-        <v>3</v>
-      </c>
-      <c r="D153" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>33</v>
+        <v>199</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
       </c>
-      <c r="D154" s="3">
-        <v>1</v>
-      </c>
+      <c r="D154" s="3"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>362</v>
+        <v>210</v>
       </c>
       <c r="C155" s="3">
-        <v>3</v>
-      </c>
-      <c r="D155" s="3">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D155" s="3"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
       </c>
       <c r="D156" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>355</v>
+        <v>15</v>
       </c>
       <c r="C157" s="3">
         <v>1</v>
       </c>
       <c r="D157" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="C158" s="3">
         <v>1</v>
       </c>
-      <c r="D158" s="3"/>
+      <c r="D158" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>251</v>
+        <v>18</v>
       </c>
       <c r="C159" s="3">
         <v>1</v>
@@ -5923,10 +5925,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>492</v>
+        <v>251</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
@@ -5935,10 +5937,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>316</v>
+        <v>492</v>
       </c>
       <c r="C161" s="3">
         <v>1</v>
@@ -5947,36 +5949,36 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="C162" s="3">
         <v>1</v>
       </c>
-      <c r="D162" s="3">
-        <v>3</v>
-      </c>
+      <c r="D162" s="3"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="C163" s="3">
         <v>1</v>
       </c>
-      <c r="D163" s="3"/>
+      <c r="D163" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="C164" s="3">
         <v>1</v>
@@ -5985,10 +5987,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5997,36 +5999,36 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>150</v>
+        <v>474</v>
       </c>
       <c r="C166" s="3">
         <v>1</v>
       </c>
-      <c r="D166" s="3">
-        <v>4</v>
-      </c>
+      <c r="D166" s="3"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C167" s="3">
         <v>1</v>
       </c>
-      <c r="D167" s="3"/>
+      <c r="D167" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C168" s="3">
         <v>1</v>
@@ -6035,10 +6037,10 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="C169" s="3">
         <v>1</v>
@@ -6047,10 +6049,10 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>483</v>
+        <v>357</v>
       </c>
       <c r="C170" s="3">
         <v>1</v>
@@ -6059,100 +6061,104 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3">
-        <v>4</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="C171" s="3">
+        <v>1</v>
+      </c>
+      <c r="D171" s="3"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C172" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="C172" s="3">
+        <v>1</v>
+      </c>
       <c r="D172" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C173" s="3"/>
+        <v>409</v>
+      </c>
+      <c r="C173" s="3">
+        <v>1</v>
+      </c>
       <c r="D173" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C174" s="3"/>
+        <v>323</v>
+      </c>
+      <c r="C174" s="3">
+        <v>1</v>
+      </c>
       <c r="D174" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3">
-        <v>3</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C175" s="3">
+        <v>1</v>
+      </c>
+      <c r="D175" s="3"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C178" s="3">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C178" s="3"/>
       <c r="D178" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -6160,7 +6166,7 @@
         <v>51</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3">
@@ -6169,10 +6175,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3">
@@ -6181,22 +6187,22 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3">
@@ -6205,46 +6211,46 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3">
@@ -6253,58 +6259,58 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3">
@@ -6313,34 +6319,34 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3">
@@ -6352,31 +6358,31 @@
         <v>49</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3">
@@ -6385,10 +6391,10 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3">
@@ -6397,10 +6403,10 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3">
@@ -6409,10 +6415,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3">
@@ -6424,19 +6430,19 @@
         <v>17</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3">
@@ -6445,10 +6451,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3">
@@ -6457,22 +6463,22 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3">
@@ -6481,10 +6487,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3">
@@ -6493,10 +6499,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3">
@@ -6505,22 +6511,22 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3">
@@ -6529,10 +6535,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3">
@@ -6541,22 +6547,22 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3">
@@ -6565,10 +6571,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3">
@@ -6577,10 +6583,10 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3">
@@ -6589,34 +6595,34 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3">
@@ -6625,48 +6631,46 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C218" s="3">
-        <v>1</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C218" s="3"/>
       <c r="D218" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>436</v>
+        <v>212</v>
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3">
@@ -6675,22 +6679,22 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>329</v>
+        <v>182</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3">
@@ -6699,34 +6703,34 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>278</v>
+        <v>436</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3">
@@ -6735,34 +6739,34 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>338</v>
+        <v>6</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3">
@@ -6771,10 +6775,10 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>30</v>
+        <v>363</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3">
@@ -6783,10 +6787,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3">
@@ -6795,10 +6799,10 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>144</v>
+        <v>338</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3">
@@ -6807,10 +6811,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>352</v>
+        <v>30</v>
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3">
@@ -6822,7 +6826,7 @@
         <v>26</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3">
@@ -6831,22 +6835,22 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>281</v>
+        <v>144</v>
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>469</v>
+        <v>352</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3">
@@ -6855,10 +6859,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3">
@@ -6867,10 +6871,10 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3">
@@ -6879,10 +6883,10 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3">
@@ -6891,10 +6895,10 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>443</v>
+        <v>348</v>
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3">
@@ -6906,7 +6910,7 @@
         <v>193</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3">
@@ -6915,10 +6919,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3">
@@ -6927,10 +6931,10 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>303</v>
+        <v>443</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3">
@@ -6938,34 +6942,64 @@
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
+      <c r="A244" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="C244" s="3"/>
-      <c r="D244" s="3"/>
+      <c r="D244" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="3"/>
-      <c r="B245" s="3"/>
+      <c r="A245" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="C245" s="3"/>
-      <c r="D245" s="3"/>
+      <c r="D245" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="3"/>
-      <c r="B246" s="3"/>
+      <c r="A246" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="C246" s="3"/>
-      <c r="D246" s="3"/>
+      <c r="D246" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
+      <c r="A247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C247" s="3"/>
-      <c r="D247" s="3"/>
+      <c r="D247" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" s="3"/>
-      <c r="B248" s="3"/>
+      <c r="A248" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>461</v>
+      </c>
       <c r="C248" s="3"/>
-      <c r="D248" s="3"/>
+      <c r="D248" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
@@ -7022,9 +7056,9 @@
       <c r="D257" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D243" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D243">
-      <sortCondition descending="1" ref="C1:C243"/>
+  <autoFilter ref="A1:D248" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
+      <sortCondition descending="1" ref="C1:C248"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1672231C-0032-41E4-B307-9F337A17F5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFBF1DC-D002-4C47-AB5C-0BF24E460295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3781,6 +3781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3804,7 +3805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -3826,13 +3827,13 @@
         <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -3888,7 +3889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -3902,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -3930,7 +3931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -3944,7 +3945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -3972,7 +3973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
@@ -3986,7 +3987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
@@ -4000,7 +4001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>44</v>
       </c>
@@ -4036,13 +4037,13 @@
         <v>83</v>
       </c>
       <c r="C18" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>44</v>
       </c>
@@ -4070,7 +4071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>51</v>
       </c>
@@ -4084,7 +4085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>119</v>
       </c>
@@ -4112,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>55</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
@@ -4140,7 +4141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>55</v>
       </c>
@@ -4154,7 +4155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -4182,7 +4183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
@@ -4196,7 +4197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>38</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>55</v>
       </c>
@@ -4222,7 +4223,7 @@
       </c>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -4250,7 +4251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>7</v>
       </c>
@@ -4264,7 +4265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>26</v>
       </c>
@@ -4292,7 +4293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>42</v>
       </c>
@@ -4306,7 +4307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>4</v>
       </c>
@@ -4320,7 +4321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>49</v>
       </c>
@@ -4334,7 +4335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
@@ -4348,7 +4349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>44</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
@@ -4376,7 +4377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>51</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
@@ -4404,7 +4405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>51</v>
       </c>
@@ -4418,7 +4419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>20</v>
       </c>
@@ -4432,7 +4433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>26</v>
       </c>
@@ -4446,7 +4447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>32</v>
       </c>
@@ -4460,7 +4461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>42</v>
       </c>
@@ -4474,7 +4475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>4</v>
       </c>
@@ -4502,7 +4503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>44</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>20</v>
       </c>
@@ -4530,7 +4531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>193</v>
       </c>
@@ -4542,7 +4543,7 @@
       </c>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
@@ -4556,7 +4557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>49</v>
       </c>
@@ -4570,7 +4571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>40</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>51</v>
       </c>
@@ -4598,7 +4599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>55</v>
       </c>
@@ -4612,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>40</v>
       </c>
@@ -4626,7 +4627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>49</v>
       </c>
@@ -4638,7 +4639,7 @@
       </c>
       <c r="D61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>38</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>44</v>
       </c>
@@ -4666,7 +4667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>119</v>
       </c>
@@ -4692,7 +4693,7 @@
       </c>
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>26</v>
       </c>
@@ -4704,7 +4705,7 @@
       </c>
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>32</v>
       </c>
@@ -4718,7 +4719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>36</v>
       </c>
@@ -4732,7 +4733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>36</v>
       </c>
@@ -4746,7 +4747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>51</v>
       </c>
@@ -4760,7 +4761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>17</v>
       </c>
@@ -4772,7 +4773,7 @@
       </c>
       <c r="D71" s="3"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>4</v>
       </c>
@@ -4800,7 +4801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>32</v>
       </c>
@@ -4814,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>40</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>40</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>193</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>193</v>
       </c>
@@ -4882,7 +4883,7 @@
       </c>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>20</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>40</v>
       </c>
@@ -4910,7 +4911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>42</v>
       </c>
@@ -4924,7 +4925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>36</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>36</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>90</v>
       </c>
@@ -4966,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>7</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>20</v>
       </c>
@@ -5008,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>7</v>
       </c>
@@ -5020,7 +5021,7 @@
       </c>
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>55</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>90</v>
       </c>
@@ -5047,7 +5048,7 @@
       </c>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>17</v>
       </c>
@@ -5059,7 +5060,7 @@
       </c>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>55</v>
       </c>
@@ -5073,7 +5074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>26</v>
       </c>
@@ -5087,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>32</v>
       </c>
@@ -5101,7 +5102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>44</v>
       </c>
@@ -5113,7 +5114,7 @@
       </c>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>32</v>
       </c>
@@ -5125,7 +5126,7 @@
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>44</v>
       </c>
@@ -5139,7 +5140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>20</v>
       </c>
@@ -5153,7 +5154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5167,7 +5168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>26</v>
       </c>
@@ -5203,9 +5204,11 @@
       <c r="C103" s="3">
         <v>2</v>
       </c>
-      <c r="D103" s="3"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D103" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>4</v>
       </c>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>119</v>
       </c>
@@ -5229,7 +5232,7 @@
       </c>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>4</v>
       </c>
@@ -5243,7 +5246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>49</v>
       </c>
@@ -5255,7 +5258,7 @@
       </c>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>26</v>
       </c>
@@ -5269,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>51</v>
       </c>
@@ -5283,7 +5286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>193</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>32</v>
       </c>
@@ -5311,7 +5314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>32</v>
       </c>
@@ -5323,7 +5326,7 @@
       </c>
       <c r="D112" s="3"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>193</v>
       </c>
@@ -5337,7 +5340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>90</v>
       </c>
@@ -5351,7 +5354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>38</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>7</v>
       </c>
@@ -5379,7 +5382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>55</v>
       </c>
@@ -5393,7 +5396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>17</v>
       </c>
@@ -5407,7 +5410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>55</v>
       </c>
@@ -5421,7 +5424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>36</v>
       </c>
@@ -5435,7 +5438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>42</v>
       </c>
@@ -5449,7 +5452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>55</v>
       </c>
@@ -5463,7 +5466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>20</v>
       </c>
@@ -5477,7 +5480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>49</v>
       </c>
@@ -5491,7 +5494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>40</v>
       </c>
@@ -5505,7 +5508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>44</v>
       </c>
@@ -5517,7 +5520,7 @@
       </c>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>42</v>
       </c>
@@ -5529,7 +5532,7 @@
       </c>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>51</v>
       </c>
@@ -5541,7 +5544,7 @@
       </c>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>32</v>
       </c>
@@ -5553,7 +5556,7 @@
       </c>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>20</v>
       </c>
@@ -5565,7 +5568,7 @@
       </c>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>40</v>
       </c>
@@ -5577,7 +5580,7 @@
       </c>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>17</v>
       </c>
@@ -5589,7 +5592,7 @@
       </c>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>55</v>
       </c>
@@ -5601,7 +5604,7 @@
       </c>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>38</v>
       </c>
@@ -5613,7 +5616,7 @@
       </c>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>119</v>
       </c>
@@ -5625,7 +5628,7 @@
       </c>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>51</v>
       </c>
@@ -5637,7 +5640,7 @@
       </c>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>17</v>
       </c>
@@ -5649,7 +5652,7 @@
       </c>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>26</v>
       </c>
@@ -5663,7 +5666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>20</v>
       </c>
@@ -5675,7 +5678,7 @@
       </c>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>38</v>
       </c>
@@ -5687,7 +5690,7 @@
       </c>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>26</v>
       </c>
@@ -5699,7 +5702,7 @@
       </c>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>26</v>
       </c>
@@ -5711,7 +5714,7 @@
       </c>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>90</v>
       </c>
@@ -5723,7 +5726,7 @@
       </c>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>40</v>
       </c>
@@ -5735,7 +5738,7 @@
       </c>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>40</v>
       </c>
@@ -5747,7 +5750,7 @@
       </c>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>90</v>
       </c>
@@ -5759,7 +5762,7 @@
       </c>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>32</v>
       </c>
@@ -5771,7 +5774,7 @@
       </c>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>7</v>
       </c>
@@ -5783,7 +5786,7 @@
       </c>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>36</v>
       </c>
@@ -5795,7 +5798,7 @@
       </c>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>119</v>
       </c>
@@ -5807,7 +5810,7 @@
       </c>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>32</v>
       </c>
@@ -5819,7 +5822,7 @@
       </c>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>32</v>
       </c>
@@ -5831,7 +5834,7 @@
       </c>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>38</v>
       </c>
@@ -5857,7 +5860,7 @@
       </c>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>193</v>
       </c>
@@ -5869,7 +5872,7 @@
       </c>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>32</v>
       </c>
@@ -5883,7 +5886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>4</v>
       </c>
@@ -5897,7 +5900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>26</v>
       </c>
@@ -5911,7 +5914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>17</v>
       </c>
@@ -5923,7 +5926,7 @@
       </c>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>4</v>
       </c>
@@ -5935,7 +5938,7 @@
       </c>
       <c r="D160" s="3"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>38</v>
       </c>
@@ -5947,7 +5950,7 @@
       </c>
       <c r="D161" s="3"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>20</v>
       </c>
@@ -5959,7 +5962,7 @@
       </c>
       <c r="D162" s="3"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>119</v>
       </c>
@@ -5985,7 +5988,7 @@
       </c>
       <c r="D164" s="3"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>119</v>
       </c>
@@ -5997,7 +6000,7 @@
       </c>
       <c r="D165" s="3"/>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>44</v>
       </c>
@@ -6009,7 +6012,7 @@
       </c>
       <c r="D166" s="3"/>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>55</v>
       </c>
@@ -6023,7 +6026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>32</v>
       </c>
@@ -6035,7 +6038,7 @@
       </c>
       <c r="D168" s="3"/>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>49</v>
       </c>
@@ -6047,7 +6050,7 @@
       </c>
       <c r="D169" s="3"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>17</v>
       </c>
@@ -6059,7 +6062,7 @@
       </c>
       <c r="D170" s="3"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>55</v>
       </c>
@@ -6071,7 +6074,7 @@
       </c>
       <c r="D171" s="3"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>42</v>
       </c>
@@ -6099,7 +6102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>40</v>
       </c>
@@ -6113,7 +6116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>40</v>
       </c>
@@ -6125,7 +6128,7 @@
       </c>
       <c r="D175" s="3"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>49</v>
       </c>
@@ -6137,7 +6140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>44</v>
       </c>
@@ -6149,7 +6152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>7</v>
       </c>
@@ -6161,7 +6164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>51</v>
       </c>
@@ -6173,7 +6176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>26</v>
       </c>
@@ -6185,7 +6188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>119</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>42</v>
       </c>
@@ -6209,7 +6212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>51</v>
       </c>
@@ -6221,7 +6224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>17</v>
       </c>
@@ -6233,7 +6236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>26</v>
       </c>
@@ -6245,7 +6248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>90</v>
       </c>
@@ -6257,7 +6260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>42</v>
       </c>
@@ -6269,7 +6272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>40</v>
       </c>
@@ -6281,7 +6284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>7</v>
       </c>
@@ -6293,7 +6296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>44</v>
       </c>
@@ -6305,7 +6308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>40</v>
       </c>
@@ -6317,7 +6320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>32</v>
       </c>
@@ -6329,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>49</v>
       </c>
@@ -6341,7 +6344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>17</v>
       </c>
@@ -6353,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>49</v>
       </c>
@@ -6365,7 +6368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>17</v>
       </c>
@@ -6377,7 +6380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>55</v>
       </c>
@@ -6389,7 +6392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>49</v>
       </c>
@@ -6401,7 +6404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>49</v>
       </c>
@@ -6413,7 +6416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>40</v>
       </c>
@@ -6425,7 +6428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>17</v>
       </c>
@@ -6437,7 +6440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>42</v>
       </c>
@@ -6449,7 +6452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>32</v>
       </c>
@@ -6461,7 +6464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>44</v>
       </c>
@@ -6473,7 +6476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>17</v>
       </c>
@@ -6485,7 +6488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>40</v>
       </c>
@@ -6497,7 +6500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>17</v>
       </c>
@@ -6509,7 +6512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>119</v>
       </c>
@@ -6521,7 +6524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>42</v>
       </c>
@@ -6533,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>42</v>
       </c>
@@ -6545,7 +6548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>40</v>
       </c>
@@ -6569,7 +6572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>4</v>
       </c>
@@ -6581,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>17</v>
       </c>
@@ -6593,7 +6596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>32</v>
       </c>
@@ -6605,7 +6608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>193</v>
       </c>
@@ -6617,7 +6620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>26</v>
       </c>
@@ -6629,7 +6632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>32</v>
       </c>
@@ -6665,7 +6668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>119</v>
       </c>
@@ -6677,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>4</v>
       </c>
@@ -6689,7 +6692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>4</v>
       </c>
@@ -6701,7 +6704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>26</v>
       </c>
@@ -6713,7 +6716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>26</v>
       </c>
@@ -6725,7 +6728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>17</v>
       </c>
@@ -6737,7 +6740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>32</v>
       </c>
@@ -6749,7 +6752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>42</v>
       </c>
@@ -6761,7 +6764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>4</v>
       </c>
@@ -6773,7 +6776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>38</v>
       </c>
@@ -6785,7 +6788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>20</v>
       </c>
@@ -6797,7 +6800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>26</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>26</v>
       </c>
@@ -6821,7 +6824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>26</v>
       </c>
@@ -6833,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>36</v>
       </c>
@@ -6845,7 +6848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>7</v>
       </c>
@@ -6857,7 +6860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>26</v>
       </c>
@@ -6869,7 +6872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>49</v>
       </c>
@@ -6881,7 +6884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>17</v>
       </c>
@@ -6893,7 +6896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>55</v>
       </c>
@@ -6905,7 +6908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>193</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>4</v>
       </c>
@@ -6941,7 +6944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>193</v>
       </c>
@@ -6953,7 +6956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>7</v>
       </c>
@@ -6965,7 +6968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>20</v>
       </c>
@@ -6977,7 +6980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>44</v>
       </c>
@@ -6989,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>36</v>
       </c>
@@ -7057,6 +7060,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D248" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Manchester_City"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
       <sortCondition descending="1" ref="C1:C248"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFBF1DC-D002-4C47-AB5C-0BF24E460295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0539FABD-8205-4F1B-8EE0-7E636CD31BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$248</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$71</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3781,7 +3781,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3805,7 +3804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -3827,13 +3826,13 @@
         <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -3841,13 +3840,13 @@
         <v>45</v>
       </c>
       <c r="C4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -3861,7 +3860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -3875,7 +3874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -3886,10 +3885,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -3903,7 +3902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -3973,7 +3972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
@@ -3987,7 +3986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
@@ -3998,127 +3997,127 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3">
         <v>9</v>
       </c>
       <c r="D18" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3">
         <v>8</v>
       </c>
       <c r="D19" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3">
         <v>8</v>
       </c>
       <c r="D20" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="3">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="C22" s="3">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="3">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" s="3">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="3">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="C24" s="3">
         <v>7</v>
@@ -4127,108 +4126,110 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="C25" s="3">
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3">
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3">
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C28" s="3">
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>6</v>
       </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C32" s="3">
         <v>6</v>
@@ -4237,40 +4238,38 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="3">
+        <v>6</v>
+      </c>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C33" s="3">
-        <v>5</v>
-      </c>
-      <c r="D33" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="C34" s="3">
         <v>5</v>
       </c>
       <c r="D34" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C35" s="3">
         <v>5</v>
@@ -4279,40 +4278,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C36" s="3">
         <v>5</v>
       </c>
       <c r="D36" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C37" s="3">
         <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
@@ -4321,7 +4320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>49</v>
       </c>
@@ -4335,68 +4334,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="3">
+        <v>5</v>
+      </c>
+      <c r="D40" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="3">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="3">
+        <v>5</v>
+      </c>
+      <c r="D42" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C40" s="3">
-        <v>4</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="3">
-        <v>4</v>
-      </c>
-      <c r="D41" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="3">
-        <v>4</v>
-      </c>
-      <c r="D42" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C43" s="3">
         <v>4</v>
       </c>
       <c r="D43" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C44" s="3">
         <v>4</v>
@@ -4405,35 +4404,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C45" s="3">
         <v>4</v>
       </c>
       <c r="D45" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C46" s="3">
         <v>4</v>
       </c>
       <c r="D46" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>26</v>
       </c>
@@ -4447,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>32</v>
       </c>
@@ -4461,7 +4460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>42</v>
       </c>
@@ -4475,7 +4474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
@@ -4489,7 +4488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>4</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>44</v>
       </c>
@@ -4517,7 +4516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>20</v>
       </c>
@@ -4528,10 +4527,10 @@
         <v>4</v>
       </c>
       <c r="D53" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>193</v>
       </c>
@@ -4543,7 +4542,7 @@
       </c>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
@@ -4557,202 +4556,202 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C56" s="3">
+        <v>4</v>
+      </c>
+      <c r="D56" s="3">
         <v>3</v>
       </c>
-      <c r="D56" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C57" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" s="3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="3">
-        <v>3</v>
       </c>
       <c r="D58" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="C59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C60" s="3">
         <v>3</v>
       </c>
       <c r="D60" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C61" s="3">
         <v>3</v>
       </c>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D61" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C62" s="3">
         <v>3</v>
       </c>
       <c r="D62" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="C63" s="3">
         <v>3</v>
       </c>
       <c r="D63" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C64" s="3">
         <v>3</v>
       </c>
-      <c r="D64" s="3">
-        <v>3</v>
-      </c>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="C65" s="3">
         <v>3</v>
       </c>
-      <c r="D65" s="3"/>
-    </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="C66" s="3">
         <v>3</v>
       </c>
-      <c r="D66" s="3"/>
-    </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="C67" s="3">
         <v>3</v>
       </c>
       <c r="D67" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
       </c>
-      <c r="D68" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="3"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="C69" s="3">
         <v>3</v>
       </c>
-      <c r="D69" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="C70" s="3">
         <v>3</v>
@@ -4761,52 +4760,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="C71" s="3">
         <v>3</v>
       </c>
-      <c r="D71" s="3"/>
-    </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="C72" s="3">
         <v>3</v>
       </c>
       <c r="D72" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="C73" s="3">
         <v>3</v>
       </c>
-      <c r="D73" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C74" s="3">
         <v>3</v>
@@ -4815,26 +4814,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="C75" s="3">
         <v>3</v>
       </c>
       <c r="D75" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="C76" s="3">
         <v>3</v>
@@ -4843,12 +4842,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C77" s="3">
         <v>3</v>
@@ -4857,52 +4856,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="C78" s="3">
         <v>3</v>
       </c>
       <c r="D78" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="C79" s="3">
         <v>3</v>
       </c>
-      <c r="D79" s="3"/>
-    </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D79" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>362</v>
+        <v>213</v>
       </c>
       <c r="C80" s="3">
         <v>3</v>
       </c>
-      <c r="D80" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>494</v>
+        <v>362</v>
       </c>
       <c r="C81" s="3">
         <v>3</v>
@@ -4911,82 +4910,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C82" s="3">
+        <v>3</v>
+      </c>
+      <c r="D82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C83" s="3">
+        <v>3</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C84" s="3">
+        <v>3</v>
+      </c>
+      <c r="D84" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B85" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C82" s="3">
-        <v>2</v>
-      </c>
-      <c r="D82" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" s="3">
-        <v>2</v>
-      </c>
-      <c r="D83" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="3">
-        <v>2</v>
-      </c>
-      <c r="D84" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="C85" s="3">
         <v>2</v>
       </c>
       <c r="D85" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
       </c>
       <c r="D86" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C87" s="3">
         <v>2</v>
@@ -4997,10 +4996,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -5009,197 +5008,199 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C89" s="3">
         <v>2</v>
       </c>
-      <c r="D89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D89" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
       </c>
-      <c r="D90" s="3"/>
+      <c r="D90" s="3">
+        <v>1</v>
+      </c>
       <c r="E90" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C91" s="3">
         <v>2</v>
       </c>
-      <c r="D91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D91" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C93" s="3">
         <v>2</v>
       </c>
-      <c r="D93" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
       </c>
-      <c r="D94" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C95" s="3">
         <v>2</v>
       </c>
-      <c r="D95" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C96" s="3">
         <v>2</v>
       </c>
-      <c r="D96" s="3"/>
-    </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="C97" s="3">
         <v>2</v>
       </c>
-      <c r="D97" s="3"/>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="C98" s="3">
         <v>2</v>
       </c>
       <c r="D98" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
       </c>
-      <c r="D99" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="C100" s="3">
         <v>2</v>
       </c>
-      <c r="D100" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C101" s="3">
         <v>2</v>
       </c>
-      <c r="D101" s="3"/>
+      <c r="D101" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="C102" s="3">
         <v>2</v>
       </c>
       <c r="D102" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C103" s="3">
         <v>2</v>
@@ -5208,256 +5209,252 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="C104" s="3">
         <v>2</v>
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>448</v>
+        <v>205</v>
       </c>
       <c r="C105" s="3">
         <v>2</v>
       </c>
-      <c r="D105" s="3"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D105" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>142</v>
+        <v>448</v>
       </c>
       <c r="C106" s="3">
         <v>2</v>
       </c>
-      <c r="D106" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D106" s="3"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C107" s="3">
         <v>2</v>
       </c>
-      <c r="D107" s="3"/>
-    </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D107" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="C108" s="3">
         <v>2</v>
       </c>
-      <c r="D108" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="C109" s="3">
         <v>2</v>
       </c>
       <c r="D109" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="C110" s="3">
         <v>2</v>
       </c>
       <c r="D110" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C111" s="3">
         <v>2</v>
       </c>
       <c r="D111" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="C112" s="3">
         <v>2</v>
       </c>
-      <c r="D112" s="3"/>
-    </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D112" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C113" s="3">
         <v>2</v>
       </c>
-      <c r="D113" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D113" s="3"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C114" s="3">
+        <v>2</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C115" s="3">
+        <v>2</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="3">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C117" s="3">
+        <v>2</v>
+      </c>
+      <c r="D117" s="3"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B118" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="3">
-        <v>1</v>
-      </c>
-      <c r="D114" s="3">
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B119" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C115" s="3">
-        <v>1</v>
-      </c>
-      <c r="D115" s="3">
+      <c r="C119" s="3">
+        <v>1</v>
+      </c>
+      <c r="D119" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B120" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C116" s="3">
-        <v>1</v>
-      </c>
-      <c r="D116" s="3">
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B121" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C117" s="3">
-        <v>1</v>
-      </c>
-      <c r="D117" s="3">
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B122" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C118" s="3">
-        <v>1</v>
-      </c>
-      <c r="D118" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C119" s="3">
-        <v>1</v>
-      </c>
-      <c r="D119" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C120" s="3">
-        <v>1</v>
-      </c>
-      <c r="D120" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C121" s="3">
-        <v>1</v>
-      </c>
-      <c r="D121" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="C122" s="3">
         <v>1</v>
@@ -5466,643 +5463,651 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C125" s="3">
+        <v>1</v>
+      </c>
+      <c r="D125" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="3">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C129" s="3">
+        <v>1</v>
+      </c>
+      <c r="D129" s="3"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C130" s="3">
+        <v>1</v>
+      </c>
+      <c r="D130" s="3"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C131" s="3">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C132" s="3">
+        <v>1</v>
+      </c>
+      <c r="D132" s="3"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C133" s="3">
+        <v>1</v>
+      </c>
+      <c r="D133" s="3"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C134" s="3">
+        <v>1</v>
+      </c>
+      <c r="D134" s="3"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C135" s="3">
+        <v>1</v>
+      </c>
+      <c r="D135" s="3"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C136" s="3">
+        <v>1</v>
+      </c>
+      <c r="D136" s="3"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C137" s="3">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C138" s="3">
+        <v>1</v>
+      </c>
+      <c r="D138" s="3"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C139" s="3">
+        <v>1</v>
+      </c>
+      <c r="D139" s="3"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C140" s="3">
+        <v>1</v>
+      </c>
+      <c r="D140" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C123" s="3">
-        <v>1</v>
-      </c>
-      <c r="D123" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C124" s="3">
-        <v>1</v>
-      </c>
-      <c r="D124" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="B141" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C141" s="3">
+        <v>1</v>
+      </c>
+      <c r="D141" s="3"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C142" s="3">
+        <v>1</v>
+      </c>
+      <c r="D142" s="3"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C143" s="3">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144" s="3">
+        <v>1</v>
+      </c>
+      <c r="D144" s="3"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C145" s="3">
+        <v>1</v>
+      </c>
+      <c r="D145" s="3"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C125" s="3">
-        <v>1</v>
-      </c>
-      <c r="D125" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C126" s="3">
-        <v>1</v>
-      </c>
-      <c r="D126" s="3"/>
-    </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C127" s="3">
-        <v>1</v>
-      </c>
-      <c r="D127" s="3"/>
-    </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C128" s="3">
-        <v>1</v>
-      </c>
-      <c r="D128" s="3"/>
-    </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="B146" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" s="3">
+        <v>1</v>
+      </c>
+      <c r="D146" s="3"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C147" s="3">
+        <v>1</v>
+      </c>
+      <c r="D147" s="3"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" s="3">
+        <v>1</v>
+      </c>
+      <c r="D148" s="3"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C129" s="3">
-        <v>1</v>
-      </c>
-      <c r="D129" s="3"/>
-    </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C130" s="3">
-        <v>1</v>
-      </c>
-      <c r="D130" s="3"/>
-    </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C131" s="3">
-        <v>1</v>
-      </c>
-      <c r="D131" s="3"/>
-    </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C132" s="3">
-        <v>1</v>
-      </c>
-      <c r="D132" s="3"/>
-    </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C133" s="3">
-        <v>1</v>
-      </c>
-      <c r="D133" s="3"/>
-    </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C134" s="3">
-        <v>1</v>
-      </c>
-      <c r="D134" s="3"/>
-    </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="B149" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C149" s="3">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C150" s="3">
+        <v>1</v>
+      </c>
+      <c r="D150" s="3"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C151" s="3">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C135" s="3">
-        <v>1</v>
-      </c>
-      <c r="D135" s="3"/>
-    </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C136" s="3">
-        <v>1</v>
-      </c>
-      <c r="D136" s="3"/>
-    </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C137" s="3">
-        <v>1</v>
-      </c>
-      <c r="D137" s="3"/>
-    </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C138" s="3">
-        <v>1</v>
-      </c>
-      <c r="D138" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C139" s="3">
-        <v>1</v>
-      </c>
-      <c r="D139" s="3"/>
-    </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C140" s="3">
-        <v>1</v>
-      </c>
-      <c r="D140" s="3"/>
-    </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C141" s="3">
-        <v>1</v>
-      </c>
-      <c r="D141" s="3"/>
-    </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C142" s="3">
-        <v>1</v>
-      </c>
-      <c r="D142" s="3"/>
-    </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C143" s="3">
-        <v>1</v>
-      </c>
-      <c r="D143" s="3"/>
-    </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C144" s="3">
-        <v>1</v>
-      </c>
-      <c r="D144" s="3"/>
-    </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C145" s="3">
-        <v>1</v>
-      </c>
-      <c r="D145" s="3"/>
-    </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C146" s="3">
-        <v>1</v>
-      </c>
-      <c r="D146" s="3"/>
-    </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="B152" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C152" s="3">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C147" s="3">
-        <v>1</v>
-      </c>
-      <c r="D147" s="3"/>
-    </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C148" s="3">
-        <v>1</v>
-      </c>
-      <c r="D148" s="3"/>
-    </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C149" s="3">
-        <v>1</v>
-      </c>
-      <c r="D149" s="3"/>
-    </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C150" s="3">
-        <v>1</v>
-      </c>
-      <c r="D150" s="3"/>
-    </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B151" s="3" t="s">
+      <c r="B153" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C151" s="3">
-        <v>1</v>
-      </c>
-      <c r="D151" s="3"/>
-    </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C152" s="3">
-        <v>1</v>
-      </c>
-      <c r="D152" s="3"/>
-    </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="C153" s="3">
         <v>1</v>
       </c>
-      <c r="D153" s="3">
-        <v>1</v>
-      </c>
+      <c r="D153" s="3"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
       </c>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C155" s="3">
+        <v>1</v>
+      </c>
+      <c r="D155" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B156" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C155" s="3">
-        <v>1</v>
-      </c>
-      <c r="D155" s="3"/>
-    </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="C156" s="3">
+        <v>1</v>
+      </c>
+      <c r="D156" s="3"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B157" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C156" s="3">
-        <v>1</v>
-      </c>
-      <c r="D156" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="C157" s="3">
+        <v>1</v>
+      </c>
+      <c r="D157" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B158" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C157" s="3">
-        <v>1</v>
-      </c>
-      <c r="D157" s="3">
+      <c r="C158" s="3">
+        <v>1</v>
+      </c>
+      <c r="D158" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B159" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C158" s="3">
-        <v>1</v>
-      </c>
-      <c r="D158" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+      <c r="C159" s="3">
+        <v>1</v>
+      </c>
+      <c r="D159" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B160" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C159" s="3">
-        <v>1</v>
-      </c>
-      <c r="D159" s="3"/>
-    </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+      <c r="C160" s="3">
+        <v>1</v>
+      </c>
+      <c r="D160" s="3"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B161" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C160" s="3">
-        <v>1</v>
-      </c>
-      <c r="D160" s="3"/>
-    </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="C161" s="3">
+        <v>1</v>
+      </c>
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B162" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C161" s="3">
-        <v>1</v>
-      </c>
-      <c r="D161" s="3"/>
-    </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="C162" s="3">
+        <v>1</v>
+      </c>
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B163" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C162" s="3">
-        <v>1</v>
-      </c>
-      <c r="D162" s="3"/>
-    </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="C163" s="3">
         <v>1</v>
       </c>
-      <c r="D163" s="3">
-        <v>3</v>
-      </c>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C164" s="3">
+        <v>1</v>
+      </c>
+      <c r="D164" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B165" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C164" s="3">
-        <v>1</v>
-      </c>
-      <c r="D164" s="3"/>
-    </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
+      <c r="C165" s="3">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B166" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C165" s="3">
-        <v>1</v>
-      </c>
-      <c r="D165" s="3"/>
-    </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+      <c r="C166" s="3">
+        <v>1</v>
+      </c>
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B167" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C166" s="3">
-        <v>1</v>
-      </c>
-      <c r="D166" s="3"/>
-    </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="C167" s="3">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B168" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C167" s="3">
-        <v>1</v>
-      </c>
-      <c r="D167" s="3">
+      <c r="C168" s="3">
+        <v>1</v>
+      </c>
+      <c r="D168" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B169" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C168" s="3">
-        <v>1</v>
-      </c>
-      <c r="D168" s="3"/>
-    </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="C169" s="3">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B170" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C169" s="3">
-        <v>1</v>
-      </c>
-      <c r="D169" s="3"/>
-    </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="C170" s="3">
+        <v>1</v>
+      </c>
+      <c r="D170" s="3"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B171" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C170" s="3">
-        <v>1</v>
-      </c>
-      <c r="D170" s="3"/>
-    </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
+      <c r="C171" s="3">
+        <v>1</v>
+      </c>
+      <c r="D171" s="3"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B172" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C171" s="3">
-        <v>1</v>
-      </c>
-      <c r="D171" s="3"/>
-    </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="C172" s="3">
         <v>1</v>
       </c>
-      <c r="D172" s="3">
-        <v>3</v>
-      </c>
+      <c r="D172" s="3"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>409</v>
+        <v>159</v>
       </c>
       <c r="C173" s="3">
         <v>1</v>
       </c>
       <c r="D173" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>40</v>
       </c>
@@ -6116,7 +6121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>40</v>
       </c>
@@ -6128,432 +6133,434 @@
       </c>
       <c r="D175" s="3"/>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C176" s="3">
+        <v>1</v>
+      </c>
+      <c r="D176" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B177" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>167</v>
+        <v>68</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3">
@@ -6562,17 +6569,17 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>4</v>
       </c>
@@ -6584,7 +6591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>17</v>
       </c>
@@ -6596,7 +6603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>32</v>
       </c>
@@ -6608,7 +6615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>193</v>
       </c>
@@ -6620,7 +6627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>26</v>
       </c>
@@ -6632,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>32</v>
       </c>
@@ -6668,7 +6675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>119</v>
       </c>
@@ -6680,7 +6687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>4</v>
       </c>
@@ -6692,7 +6699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>4</v>
       </c>
@@ -6704,7 +6711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>26</v>
       </c>
@@ -6716,7 +6723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>26</v>
       </c>
@@ -6728,7 +6735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>17</v>
       </c>
@@ -6740,7 +6747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>32</v>
       </c>
@@ -6752,7 +6759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>42</v>
       </c>
@@ -6764,7 +6771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>4</v>
       </c>
@@ -6776,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>38</v>
       </c>
@@ -6788,7 +6795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>20</v>
       </c>
@@ -6800,7 +6807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>26</v>
       </c>
@@ -6812,7 +6819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>26</v>
       </c>
@@ -6824,7 +6831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>26</v>
       </c>
@@ -6836,7 +6843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>36</v>
       </c>
@@ -6848,7 +6855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>7</v>
       </c>
@@ -6860,7 +6867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>26</v>
       </c>
@@ -6872,7 +6879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>49</v>
       </c>
@@ -6884,7 +6891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>17</v>
       </c>
@@ -6896,7 +6903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>55</v>
       </c>
@@ -6908,7 +6915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>193</v>
       </c>
@@ -6920,7 +6927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>4</v>
       </c>
@@ -6929,7 +6936,7 @@
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -6944,7 +6951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>193</v>
       </c>
@@ -6956,7 +6963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>7</v>
       </c>
@@ -6968,7 +6975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>20</v>
       </c>
@@ -6980,7 +6987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>44</v>
       </c>
@@ -6992,7 +6999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>36</v>
       </c>
@@ -7060,11 +7067,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D248" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Manchester_City"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
       <sortCondition descending="1" ref="C1:C248"/>
     </sortState>
@@ -11489,7 +11491,7 @@
         <v>194</v>
       </c>
       <c r="C13" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -11505,7 +11507,9 @@
       <c r="C14" s="6">
         <v>2</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -11515,7 +11519,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="6">
         <v>2</v>
@@ -11619,7 +11623,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -11807,9 +11811,11 @@
         <v>197</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
@@ -11832,7 +11838,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -12150,39 +12156,77 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
+      <c r="A67" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="6">
+        <v>2</v>
+      </c>
       <c r="D67" s="6"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
+      <c r="A68" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="6">
+        <v>1</v>
+      </c>
+      <c r="D68" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="D69" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
+      <c r="A70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
+      <c r="D70" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
+      <c r="A71" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C71" s="6">
+        <v>2</v>
+      </c>
       <c r="D71" s="6"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
+      <c r="A72" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="6">
+        <v>1</v>
+      </c>
       <c r="D72" s="6"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -13254,7 +13298,7 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D64" xr:uid="{00000000-0009-0000-0000-000004000000}">
+  <autoFilter ref="A1:D71" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
       <sortCondition descending="1" ref="C1:C50"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0539FABD-8205-4F1B-8EE0-7E636CD31BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CA0418-3E33-410A-8412-4BC4C67E53C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$248</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$77</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -11316,6 +11316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11339,7 +11340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -11364,10 +11365,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>51</v>
       </c>
@@ -11389,11 +11390,11 @@
         <v>121</v>
       </c>
       <c r="C5" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -11405,7 +11406,7 @@
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
@@ -11419,7 +11420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -11431,7 +11432,7 @@
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
@@ -11443,7 +11444,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>36</v>
       </c>
@@ -11455,7 +11456,7 @@
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>55</v>
       </c>
@@ -11469,7 +11470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
@@ -11483,7 +11484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>193</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>193</v>
       </c>
@@ -11511,7 +11512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>4</v>
       </c>
@@ -11525,7 +11526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>4</v>
       </c>
@@ -11537,7 +11538,7 @@
       </c>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>7</v>
       </c>
@@ -11549,7 +11550,7 @@
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>4</v>
       </c>
@@ -11561,7 +11562,7 @@
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
@@ -11573,7 +11574,7 @@
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
@@ -11587,7 +11588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>17</v>
       </c>
@@ -11601,7 +11602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>26</v>
       </c>
@@ -11615,7 +11616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
@@ -11629,7 +11630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
@@ -11641,7 +11642,7 @@
       </c>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -11653,7 +11654,7 @@
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>17</v>
       </c>
@@ -11665,7 +11666,7 @@
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>51</v>
       </c>
@@ -11679,7 +11680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>17</v>
       </c>
@@ -11691,7 +11692,7 @@
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>51</v>
       </c>
@@ -11717,7 +11718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>36</v>
       </c>
@@ -11729,7 +11730,7 @@
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>55</v>
       </c>
@@ -11741,7 +11742,7 @@
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
@@ -11753,7 +11754,7 @@
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>55</v>
       </c>
@@ -11765,7 +11766,7 @@
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>193</v>
       </c>
@@ -11777,7 +11778,7 @@
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>42</v>
       </c>
@@ -11789,7 +11790,7 @@
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>42</v>
       </c>
@@ -11803,7 +11804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>193</v>
       </c>
@@ -11817,7 +11818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>42</v>
       </c>
@@ -11829,7 +11830,7 @@
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>4</v>
       </c>
@@ -11841,7 +11842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>7</v>
       </c>
@@ -11853,7 +11854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>4</v>
       </c>
@@ -11865,7 +11866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>7</v>
       </c>
@@ -11877,7 +11878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>7</v>
       </c>
@@ -11889,7 +11890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>17</v>
       </c>
@@ -11901,7 +11902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>20</v>
       </c>
@@ -11913,7 +11914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>20</v>
       </c>
@@ -11925,7 +11926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>26</v>
       </c>
@@ -11937,7 +11938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -11949,7 +11950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>32</v>
       </c>
@@ -11961,7 +11962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>51</v>
       </c>
@@ -11973,7 +11974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>36</v>
       </c>
@@ -11985,7 +11986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>36</v>
       </c>
@@ -11997,7 +11998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>36</v>
       </c>
@@ -12016,12 +12017,14 @@
       <c r="B55" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="C55" s="6"/>
+      <c r="C55" s="6">
+        <v>1</v>
+      </c>
       <c r="D55" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
@@ -12033,7 +12036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
@@ -12045,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>193</v>
       </c>
@@ -12057,7 +12060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
@@ -12069,7 +12072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>193</v>
       </c>
@@ -12081,7 +12084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>42</v>
       </c>
@@ -12093,7 +12096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>44</v>
       </c>
@@ -12105,7 +12108,7 @@
       </c>
       <c r="D62" s="6"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>44</v>
       </c>
@@ -12117,7 +12120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>44</v>
       </c>
@@ -12129,7 +12132,7 @@
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>49</v>
       </c>
@@ -12141,7 +12144,7 @@
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>49</v>
       </c>
@@ -12155,7 +12158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
@@ -12167,7 +12170,7 @@
       </c>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
@@ -12181,7 +12184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>69</v>
       </c>
@@ -12193,7 +12196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>26</v>
       </c>
@@ -12205,7 +12208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>26</v>
       </c>
@@ -12217,7 +12220,7 @@
       </c>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>4</v>
       </c>
@@ -12230,33 +12233,63 @@
       <c r="D72" s="6"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
+      <c r="A73" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>464</v>
+      </c>
       <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
+      <c r="D73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="6">
+        <v>3</v>
+      </c>
       <c r="D74" s="6"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
+      <c r="D75" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>348</v>
+      </c>
       <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
+      <c r="D76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="6">
+        <v>1</v>
+      </c>
       <c r="D77" s="6"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -13298,7 +13331,12 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D71" xr:uid="{00000000-0009-0000-0000-000004000000}">
+  <autoFilter ref="A1:D77" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="AC_Milan"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
       <sortCondition descending="1" ref="C1:C50"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CA0418-3E33-410A-8412-4BC4C67E53C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E62822-1296-4EDE-BB8F-93CDC33459ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$248</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -11316,7 +11316,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11340,7 +11339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -11362,13 +11361,13 @@
         <v>120</v>
       </c>
       <c r="C3" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>51</v>
       </c>
@@ -11376,10 +11375,10 @@
         <v>52</v>
       </c>
       <c r="C4" s="6">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6">
         <v>3</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -11390,11 +11389,11 @@
         <v>121</v>
       </c>
       <c r="C5" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -11406,7 +11405,7 @@
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
@@ -11420,7 +11419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -11432,7 +11431,7 @@
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
@@ -11440,11 +11439,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>36</v>
       </c>
@@ -11456,7 +11457,7 @@
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>55</v>
       </c>
@@ -11470,7 +11471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
@@ -11484,7 +11485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>193</v>
       </c>
@@ -11498,7 +11499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>193</v>
       </c>
@@ -11512,7 +11513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>4</v>
       </c>
@@ -11526,7 +11527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>4</v>
       </c>
@@ -11538,7 +11539,7 @@
       </c>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>7</v>
       </c>
@@ -11550,7 +11551,7 @@
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>4</v>
       </c>
@@ -11562,7 +11563,7 @@
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
@@ -11574,7 +11575,7 @@
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
@@ -11588,7 +11589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>17</v>
       </c>
@@ -11602,7 +11603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>26</v>
       </c>
@@ -11616,7 +11617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
@@ -11630,7 +11631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
@@ -11642,7 +11643,7 @@
       </c>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -11654,7 +11655,7 @@
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>17</v>
       </c>
@@ -11666,7 +11667,7 @@
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>51</v>
       </c>
@@ -11674,13 +11675,13 @@
         <v>74</v>
       </c>
       <c r="C27" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>17</v>
       </c>
@@ -11692,7 +11693,7 @@
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>51</v>
       </c>
@@ -11712,13 +11713,13 @@
         <v>131</v>
       </c>
       <c r="C30" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>36</v>
       </c>
@@ -11730,7 +11731,7 @@
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>55</v>
       </c>
@@ -11742,7 +11743,7 @@
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
@@ -11754,7 +11755,7 @@
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>55</v>
       </c>
@@ -11766,7 +11767,7 @@
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>193</v>
       </c>
@@ -11778,7 +11779,7 @@
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>42</v>
       </c>
@@ -11790,7 +11791,7 @@
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>42</v>
       </c>
@@ -11804,7 +11805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>193</v>
       </c>
@@ -11818,7 +11819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>42</v>
       </c>
@@ -11830,7 +11831,7 @@
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>4</v>
       </c>
@@ -11842,7 +11843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>7</v>
       </c>
@@ -11854,7 +11855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>4</v>
       </c>
@@ -11866,7 +11867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>7</v>
       </c>
@@ -11878,7 +11879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>7</v>
       </c>
@@ -11890,7 +11891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>17</v>
       </c>
@@ -11902,7 +11903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>20</v>
       </c>
@@ -11914,7 +11915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>20</v>
       </c>
@@ -11926,7 +11927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>26</v>
       </c>
@@ -11938,7 +11939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -11950,7 +11951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>32</v>
       </c>
@@ -11962,19 +11963,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C51" s="6"/>
+      <c r="C51" s="6">
+        <v>1</v>
+      </c>
       <c r="D51" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>36</v>
       </c>
@@ -11986,7 +11989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>36</v>
       </c>
@@ -11998,7 +12001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>36</v>
       </c>
@@ -12021,10 +12024,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
@@ -12036,7 +12039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
@@ -12048,7 +12051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>193</v>
       </c>
@@ -12060,7 +12063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
@@ -12072,7 +12075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>193</v>
       </c>
@@ -12084,7 +12087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>42</v>
       </c>
@@ -12096,7 +12099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>44</v>
       </c>
@@ -12108,7 +12111,7 @@
       </c>
       <c r="D62" s="6"/>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>44</v>
       </c>
@@ -12120,7 +12123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>44</v>
       </c>
@@ -12132,7 +12135,7 @@
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>49</v>
       </c>
@@ -12144,7 +12147,7 @@
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>49</v>
       </c>
@@ -12158,7 +12161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>69</v>
       </c>
@@ -12170,7 +12173,7 @@
       </c>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
@@ -12184,7 +12187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>69</v>
       </c>
@@ -12196,7 +12199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>26</v>
       </c>
@@ -12208,7 +12211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>26</v>
       </c>
@@ -12220,7 +12223,7 @@
       </c>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>4</v>
       </c>
@@ -12241,10 +12244,10 @@
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>55</v>
       </c>
@@ -12256,7 +12259,7 @@
       </c>
       <c r="D74" s="6"/>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>55</v>
       </c>
@@ -12268,7 +12271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>55</v>
       </c>
@@ -12280,7 +12283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>55</v>
       </c>
@@ -12293,28 +12296,52 @@
       <c r="D77" s="6"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
+      <c r="A78" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="D78" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>132</v>
+      </c>
       <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
+      <c r="D79" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>292</v>
+      </c>
       <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
+      <c r="D80" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
+      <c r="A81" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>434</v>
+      </c>
       <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
+      <c r="D81" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
@@ -13331,12 +13358,7 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D77" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="AC_Milan"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:D80" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
       <sortCondition descending="1" ref="C1:C50"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E62822-1296-4EDE-BB8F-93CDC33459ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8096B0F8-B07E-46DC-81EF-A7367F4BAD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -9434,7 +9434,7 @@
         <v>200</v>
       </c>
       <c r="C34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3"/>
     </row>
@@ -10149,7 +10149,9 @@
       <c r="B91" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="3"/>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
       <c r="D91" s="3">
         <v>2</v>
       </c>
@@ -10462,7 +10464,9 @@
       <c r="C116" s="3">
         <v>2</v>
       </c>
-      <c r="D116" s="3"/>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
@@ -10513,15 +10517,27 @@
       <c r="D120" s="3"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
+      <c r="A121" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
+      <c r="D121" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
+      <c r="A122" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
       <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -11341,128 +11357,130 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="C2" s="6">
         <v>5</v>
       </c>
       <c r="D2" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
         <v>5</v>
-      </c>
-      <c r="D3" s="6">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="6">
-        <v>10</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C4" s="6"/>
       <c r="D4" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C5" s="6">
-        <v>6</v>
-      </c>
-      <c r="D5" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>8</v>
+        <v>301</v>
       </c>
       <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>213</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C9" s="6">
         <v>3</v>
       </c>
       <c r="D9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>104</v>
+        <v>426</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>426</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6">
         <v>2</v>
@@ -11473,117 +11491,121 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>494</v>
+        <v>448</v>
       </c>
       <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
         <v>2</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="6">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C13" s="6"/>
       <c r="D13" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="6">
+        <v>464</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6">
         <v>2</v>
-      </c>
-      <c r="D14" s="6">
-        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="6">
-        <v>2</v>
-      </c>
       <c r="D15" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C18" s="6">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>494</v>
       </c>
       <c r="C20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -11591,13 +11613,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="C21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -11605,13 +11627,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="C22" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -11619,13 +11641,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C23" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -11633,222 +11655,224 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C25" s="6">
         <v>1</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="C27" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="6">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C30" s="6"/>
       <c r="D30" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="6">
-        <v>1</v>
-      </c>
-      <c r="D32" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="6">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1</v>
-      </c>
-      <c r="D34" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="6">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C37" s="6"/>
       <c r="D37" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C38" s="6"/>
       <c r="D38" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C39" s="6">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>6</v>
+        <v>283</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6">
@@ -11857,10 +11881,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>11</v>
+        <v>339</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6">
@@ -11869,10 +11893,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>14</v>
+        <v>491</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6">
@@ -11881,10 +11905,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -11893,10 +11917,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6">
@@ -11905,10 +11929,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6">
@@ -11917,10 +11941,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6">
@@ -11929,22 +11953,22 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>30</v>
+        <v>348</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6">
@@ -11953,10 +11977,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6">
@@ -11968,21 +11992,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C51" s="6"/>
       <c r="D51" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6">
@@ -11991,10 +12013,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6">
@@ -12003,108 +12025,106 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C54" s="6">
+        <v>6</v>
+      </c>
+      <c r="D54" s="6"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>448</v>
+        <v>56</v>
       </c>
       <c r="C55" s="6">
-        <v>1</v>
-      </c>
-      <c r="D55" s="6">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D55" s="6"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C56" s="6">
+        <v>2</v>
+      </c>
+      <c r="D56" s="6"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C57" s="6">
+        <v>2</v>
+      </c>
+      <c r="D57" s="6"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6">
-        <v>3</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C58" s="6">
+        <v>2</v>
+      </c>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C59" s="6">
+        <v>2</v>
+      </c>
+      <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6">
-        <v>1</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="C60" s="6">
+        <v>2</v>
+      </c>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -12113,22 +12133,22 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6">
-        <v>1</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C63" s="6">
+        <v>1</v>
+      </c>
+      <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -12137,10 +12157,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C65" s="6">
         <v>1</v>
@@ -12149,86 +12169,82 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
       </c>
-      <c r="D66" s="6">
-        <v>1</v>
-      </c>
+      <c r="D66" s="6"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="C67" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="6"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
       </c>
-      <c r="D68" s="6">
-        <v>1</v>
-      </c>
+      <c r="D68" s="6"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6">
-        <v>1</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="C69" s="6">
+        <v>1</v>
+      </c>
+      <c r="D69" s="6"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6">
-        <v>4</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C70" s="6">
+        <v>1</v>
+      </c>
+      <c r="D70" s="6"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>355</v>
+        <v>62</v>
       </c>
       <c r="C71" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="6"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -12237,58 +12253,58 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6">
-        <v>2</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C73" s="6">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="C74" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" s="6"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C75" s="6">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6">
-        <v>1</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C76" s="6">
+        <v>1</v>
+      </c>
+      <c r="D76" s="6"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="C77" s="6">
         <v>1</v>
@@ -12297,51 +12313,51 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C78" s="6">
+        <v>1</v>
+      </c>
+      <c r="D78" s="6"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
+      <c r="D79" s="6"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6">
-        <v>1</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C80" s="6">
+        <v>1</v>
+      </c>
+      <c r="D80" s="6"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C81" s="6">
+        <v>1</v>
+      </c>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
@@ -13359,8 +13375,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D80" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D61">
-      <sortCondition descending="1" ref="C1:C50"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D81">
+      <sortCondition descending="1" ref="D1:D80"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8096B0F8-B07E-46DC-81EF-A7367F4BAD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8665B5D-71AB-4141-A3EA-2097B9152AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$252</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3826,7 +3826,7 @@
         <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
@@ -4008,7 +4008,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -4078,10 +4078,10 @@
         <v>81</v>
       </c>
       <c r="C21" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4120,10 +4120,10 @@
         <v>89</v>
       </c>
       <c r="C24" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4314,7 +4314,7 @@
         <v>106</v>
       </c>
       <c r="C38" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D38" s="3">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>5</v>
       </c>
       <c r="D42" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -4398,7 +4398,7 @@
         <v>68</v>
       </c>
       <c r="C44" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
@@ -4702,7 +4702,7 @@
         <v>115</v>
       </c>
       <c r="C66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" s="3">
         <v>2</v>
@@ -5175,7 +5175,7 @@
         <v>155</v>
       </c>
       <c r="C101" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D101" s="3">
         <v>9</v>
@@ -5557,7 +5557,9 @@
       <c r="C129" s="3">
         <v>1</v>
       </c>
-      <c r="D129" s="3"/>
+      <c r="D129" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
@@ -5925,7 +5927,7 @@
         <v>355</v>
       </c>
       <c r="C159" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D159" s="3">
         <v>1</v>
@@ -6168,7 +6170,7 @@
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -7012,27 +7014,51 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" s="3"/>
-      <c r="B249" s="3"/>
-      <c r="C249" s="3"/>
+      <c r="A249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C249" s="3">
+        <v>1</v>
+      </c>
       <c r="D249" s="3"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="3"/>
-      <c r="B250" s="3"/>
+      <c r="A250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>416</v>
+      </c>
       <c r="C250" s="3"/>
-      <c r="D250" s="3"/>
+      <c r="D250" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251" s="3"/>
-      <c r="B251" s="3"/>
-      <c r="C251" s="3"/>
+      <c r="A251" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C251" s="3">
+        <v>1</v>
+      </c>
       <c r="D251" s="3"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" s="3"/>
-      <c r="B252" s="3"/>
-      <c r="C252" s="3"/>
+      <c r="A252" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C252" s="3">
+        <v>1</v>
+      </c>
       <c r="D252" s="3"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -7066,7 +7092,7 @@
       <c r="D257" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D248" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:D252" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
       <sortCondition descending="1" ref="C1:C248"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8665B5D-71AB-4141-A3EA-2097B9152AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7490922F-E1CC-473F-8F29-F6118EB781DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$251</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="1080">
   <si>
     <t>Equipo</t>
   </si>
@@ -3781,7 +3781,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E257"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3804,7 +3805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>69</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -3840,13 +3841,13 @@
         <v>45</v>
       </c>
       <c r="C4" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -3882,60 +3883,60 @@
         <v>10</v>
       </c>
       <c r="C7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" s="3">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="3">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="C11" s="3">
         <v>11</v>
@@ -3944,32 +3945,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -3980,228 +3981,228 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C16" s="3">
         <v>10</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D16" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="3">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="3">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D19" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C20" s="3">
         <v>9</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D20" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="3">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="3">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3">
         <v>8</v>
       </c>
       <c r="D22" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>214</v>
+        <v>53</v>
       </c>
       <c r="C23" s="3">
         <v>8</v>
       </c>
       <c r="D23" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="C24" s="3">
         <v>8</v>
       </c>
       <c r="D24" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="3">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="3">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C25" s="3">
-        <v>7</v>
-      </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="3">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C27" s="3">
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3">
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C29" s="3">
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C30" s="3">
         <v>7</v>
@@ -4210,150 +4211,150 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="C31" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C32" s="3">
-        <v>6</v>
-      </c>
-      <c r="D32" s="3">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C33" s="3">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="3">
         <v>6</v>
       </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="3">
-        <v>5</v>
-      </c>
       <c r="D34" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C35" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="3">
+        <v>6</v>
+      </c>
+      <c r="D36" s="3">
         <v>7</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="3">
-        <v>5</v>
-      </c>
-      <c r="D36" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C37" s="3">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="3">
         <v>5</v>
       </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="3">
-        <v>8</v>
-      </c>
       <c r="D38" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C40" s="3">
         <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C41" s="3">
         <v>5</v>
@@ -4362,35 +4363,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="C42" s="3">
         <v>5</v>
       </c>
       <c r="D42" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="3">
+        <v>5</v>
+      </c>
+      <c r="D43" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="3">
-        <v>4</v>
-      </c>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
@@ -4404,7 +4405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -4412,32 +4413,32 @@
         <v>71</v>
       </c>
       <c r="C45" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="C46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C47" s="3">
         <v>4</v>
@@ -4446,12 +4447,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>342</v>
+        <v>85</v>
       </c>
       <c r="C48" s="3">
         <v>4</v>
@@ -4460,108 +4461,108 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>353</v>
+        <v>28</v>
       </c>
       <c r="C49" s="3">
         <v>4</v>
       </c>
       <c r="D49" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>92</v>
+        <v>342</v>
       </c>
       <c r="C50" s="3">
         <v>4</v>
       </c>
       <c r="D50" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>249</v>
+        <v>353</v>
       </c>
       <c r="C51" s="3">
         <v>4</v>
       </c>
       <c r="D51" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="C52" s="3">
         <v>4</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>87</v>
+        <v>216</v>
       </c>
       <c r="C53" s="3">
         <v>4</v>
       </c>
       <c r="D53" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="C54" s="3">
         <v>4</v>
       </c>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D54" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C55" s="3">
         <v>4</v>
       </c>
-      <c r="D55" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D55" s="3"/>
+    </row>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="C56" s="3">
         <v>4</v>
@@ -4570,26 +4571,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C57" s="3">
         <v>4</v>
       </c>
       <c r="D57" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3">
         <v>4</v>
@@ -4598,57 +4599,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="C59" s="3">
         <v>4</v>
       </c>
       <c r="D59" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="C60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="C61" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C62" s="3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="3">
-        <v>3</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -4656,184 +4657,186 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C63" s="3">
         <v>3</v>
       </c>
       <c r="D63" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C64" s="3">
         <v>3</v>
       </c>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D64" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C65" s="3">
         <v>3</v>
       </c>
       <c r="D65" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="C66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C67" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D67" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
       </c>
-      <c r="D68" s="3"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D68" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="C69" s="3">
         <v>3</v>
       </c>
-      <c r="D69" s="3"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D69" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="C70" s="3">
         <v>3</v>
       </c>
-      <c r="D70" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="C71" s="3">
         <v>3</v>
       </c>
-      <c r="D71" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D71" s="3"/>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="C72" s="3">
         <v>3</v>
       </c>
       <c r="D72" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="C73" s="3">
         <v>3</v>
       </c>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D73" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="C74" s="3">
         <v>3</v>
       </c>
       <c r="D74" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="C75" s="3">
         <v>3</v>
       </c>
-      <c r="D75" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D75" s="3"/>
+    </row>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C76" s="3">
         <v>3</v>
@@ -4842,26 +4845,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="C77" s="3">
         <v>3</v>
       </c>
       <c r="D77" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="C78" s="3">
         <v>3</v>
@@ -4870,12 +4873,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C79" s="3">
         <v>3</v>
@@ -4884,24 +4887,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="C80" s="3">
         <v>3</v>
       </c>
-      <c r="D80" s="3"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D80" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>362</v>
+        <v>98</v>
       </c>
       <c r="C81" s="3">
         <v>3</v>
@@ -4910,26 +4915,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>494</v>
+        <v>213</v>
       </c>
       <c r="C82" s="3">
         <v>3</v>
       </c>
-      <c r="D82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>206</v>
+        <v>362</v>
       </c>
       <c r="C83" s="3">
         <v>3</v>
@@ -4938,113 +4941,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>409</v>
+        <v>494</v>
       </c>
       <c r="C84" s="3">
         <v>3</v>
       </c>
       <c r="D84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C85" s="3">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C86" s="3">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="3">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="3">
+        <v>3</v>
+      </c>
+      <c r="D88" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C85" s="3">
-        <v>2</v>
-      </c>
-      <c r="D85" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" s="3">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" s="3">
-        <v>2</v>
-      </c>
-      <c r="D87" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" s="3">
-        <v>2</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C89" s="3">
         <v>2</v>
       </c>
       <c r="D89" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C90" s="3">
         <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C91" s="3">
         <v>2</v>
@@ -5053,206 +5056,208 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3">
         <v>2</v>
       </c>
-      <c r="D93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
       </c>
-      <c r="D94" s="3"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C95" s="3">
         <v>2</v>
       </c>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D95" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="C96" s="3">
         <v>2</v>
       </c>
-      <c r="D96" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C97" s="3">
         <v>2</v>
       </c>
-      <c r="D97" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C98" s="3">
         <v>2</v>
       </c>
-      <c r="D98" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
       </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="C100" s="3">
         <v>2</v>
       </c>
-      <c r="D100" s="3"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D100" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" s="3">
+        <v>2</v>
+      </c>
+      <c r="D101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="3">
-        <v>4</v>
-      </c>
-      <c r="D101" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="B102" s="3" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C102" s="3">
         <v>2</v>
       </c>
-      <c r="D102" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="C103" s="3">
         <v>2</v>
       </c>
-      <c r="D103" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="C104" s="3">
         <v>2</v>
       </c>
-      <c r="D104" s="3"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D104" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C105" s="3">
         <v>2</v>
       </c>
       <c r="D105" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>448</v>
+        <v>200</v>
       </c>
       <c r="C106" s="3">
         <v>2</v>
       </c>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="C107" s="3">
         <v>2</v>
@@ -5261,106 +5266,104 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>126</v>
+        <v>448</v>
       </c>
       <c r="C108" s="3">
         <v>2</v>
       </c>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="C109" s="3">
         <v>2</v>
       </c>
       <c r="D109" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C110" s="3">
         <v>2</v>
       </c>
-      <c r="D110" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="C111" s="3">
         <v>2</v>
       </c>
       <c r="D111" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C112" s="3">
         <v>2</v>
       </c>
       <c r="D112" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="C113" s="3">
         <v>2</v>
       </c>
-      <c r="D113" s="3"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D113" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C114" s="3">
         <v>2</v>
       </c>
-      <c r="D114" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D114" s="3"/>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>113</v>
+        <v>198</v>
       </c>
       <c r="C115" s="3">
         <v>2</v>
@@ -5369,778 +5372,784 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C116" s="3">
         <v>2</v>
       </c>
-      <c r="D116" s="3"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="C117" s="3">
         <v>2</v>
       </c>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C118" s="3">
+        <v>2</v>
+      </c>
+      <c r="D118" s="3"/>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C119" s="3">
+        <v>2</v>
+      </c>
+      <c r="D119" s="3"/>
+    </row>
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C120" s="3">
+        <v>2</v>
+      </c>
+      <c r="D120" s="3"/>
+    </row>
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B121" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="3">
-        <v>1</v>
-      </c>
-      <c r="D118" s="3">
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B122" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C119" s="3">
-        <v>1</v>
-      </c>
-      <c r="D119" s="3">
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B123" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C120" s="3">
-        <v>1</v>
-      </c>
-      <c r="D120" s="3">
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B124" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C121" s="3">
-        <v>1</v>
-      </c>
-      <c r="D121" s="3">
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B125" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C122" s="3">
-        <v>1</v>
-      </c>
-      <c r="D122" s="3">
+      <c r="C125" s="3">
+        <v>1</v>
+      </c>
+      <c r="D125" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C123" s="3">
-        <v>1</v>
-      </c>
-      <c r="D123" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C124" s="3">
-        <v>1</v>
-      </c>
-      <c r="D124" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C125" s="3">
-        <v>1</v>
-      </c>
-      <c r="D125" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C127" s="3">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C126" s="3">
-        <v>1</v>
-      </c>
-      <c r="D126" s="3">
+      <c r="C129" s="3">
+        <v>1</v>
+      </c>
+      <c r="D129" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C127" s="3">
-        <v>1</v>
-      </c>
-      <c r="D127" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C128" s="3">
-        <v>1</v>
-      </c>
-      <c r="D128" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C129" s="3">
-        <v>1</v>
-      </c>
-      <c r="D129" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C130" s="3">
+        <v>2</v>
+      </c>
+      <c r="D130" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C131" s="3">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C132" s="3">
+        <v>1</v>
+      </c>
+      <c r="D132" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B133" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C130" s="3">
-        <v>1</v>
-      </c>
-      <c r="D130" s="3"/>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="C133" s="3">
+        <v>1</v>
+      </c>
+      <c r="D133" s="3"/>
+    </row>
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B134" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C131" s="3">
-        <v>1</v>
-      </c>
-      <c r="D131" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="C134" s="3">
+        <v>1</v>
+      </c>
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B135" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C132" s="3">
-        <v>1</v>
-      </c>
-      <c r="D132" s="3"/>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="C135" s="3">
+        <v>1</v>
+      </c>
+      <c r="D135" s="3"/>
+    </row>
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B136" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C133" s="3">
-        <v>1</v>
-      </c>
-      <c r="D133" s="3"/>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="C136" s="3">
+        <v>2</v>
+      </c>
+      <c r="D136" s="3"/>
+    </row>
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B137" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C134" s="3">
-        <v>1</v>
-      </c>
-      <c r="D134" s="3"/>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="C137" s="3">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3"/>
+    </row>
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B138" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C135" s="3">
-        <v>1</v>
-      </c>
-      <c r="D135" s="3"/>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="C138" s="3">
+        <v>1</v>
+      </c>
+      <c r="D138" s="3"/>
+    </row>
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B139" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C136" s="3">
-        <v>1</v>
-      </c>
-      <c r="D136" s="3"/>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="C139" s="3">
+        <v>1</v>
+      </c>
+      <c r="D139" s="3"/>
+    </row>
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B140" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C137" s="3">
-        <v>1</v>
-      </c>
-      <c r="D137" s="3"/>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="C140" s="3">
+        <v>1</v>
+      </c>
+      <c r="D140" s="3"/>
+    </row>
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B141" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C138" s="3">
-        <v>1</v>
-      </c>
-      <c r="D138" s="3"/>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="C141" s="3">
+        <v>1</v>
+      </c>
+      <c r="D141" s="3"/>
+    </row>
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B142" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C139" s="3">
-        <v>1</v>
-      </c>
-      <c r="D139" s="3"/>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C140" s="3">
-        <v>1</v>
-      </c>
-      <c r="D140" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C141" s="3">
-        <v>1</v>
-      </c>
-      <c r="D141" s="3"/>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="C142" s="3">
         <v>1</v>
       </c>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C143" s="3">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C144" s="3">
+        <v>1</v>
+      </c>
+      <c r="D144" s="3"/>
+    </row>
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C145" s="3">
+        <v>1</v>
+      </c>
+      <c r="D145" s="3"/>
+    </row>
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C143" s="3">
-        <v>1</v>
-      </c>
-      <c r="D143" s="3"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="C146" s="3">
+        <v>1</v>
+      </c>
+      <c r="D146" s="3"/>
+    </row>
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B147" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C144" s="3">
-        <v>1</v>
-      </c>
-      <c r="D144" s="3"/>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C145" s="3">
-        <v>1</v>
-      </c>
-      <c r="D145" s="3"/>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C146" s="3">
-        <v>1</v>
-      </c>
-      <c r="D146" s="3"/>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="C147" s="3">
         <v>1</v>
       </c>
-      <c r="D147" s="3"/>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D147" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C148" s="3">
+        <v>1</v>
+      </c>
+      <c r="D148" s="3"/>
+    </row>
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C148" s="3">
-        <v>1</v>
-      </c>
-      <c r="D148" s="3"/>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="C149" s="3">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3"/>
+    </row>
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B150" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C149" s="3">
-        <v>1</v>
-      </c>
-      <c r="D149" s="3"/>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
+      <c r="C150" s="3">
+        <v>1</v>
+      </c>
+      <c r="D150" s="3"/>
+    </row>
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B151" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C150" s="3">
-        <v>1</v>
-      </c>
-      <c r="D150" s="3"/>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="C151" s="3">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3"/>
+    </row>
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B152" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C151" s="3">
-        <v>1</v>
-      </c>
-      <c r="D151" s="3"/>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="C152" s="3">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3"/>
+    </row>
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B153" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C152" s="3">
-        <v>1</v>
-      </c>
-      <c r="D152" s="3"/>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="C153" s="3">
         <v>1</v>
       </c>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="3">
+        <v>1</v>
+      </c>
+      <c r="D154" s="3"/>
+    </row>
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C154" s="3">
-        <v>1</v>
-      </c>
-      <c r="D154" s="3"/>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
+      <c r="C155" s="3">
+        <v>1</v>
+      </c>
+      <c r="D155" s="3"/>
+    </row>
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B156" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C155" s="3">
-        <v>1</v>
-      </c>
-      <c r="D155" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="C156" s="3">
+        <v>1</v>
+      </c>
+      <c r="D156" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B157" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C156" s="3">
-        <v>1</v>
-      </c>
-      <c r="D156" s="3"/>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="C157" s="3">
+        <v>1</v>
+      </c>
+      <c r="D157" s="3"/>
+    </row>
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B158" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C157" s="3">
-        <v>1</v>
-      </c>
-      <c r="D157" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+      <c r="C158" s="3">
+        <v>1</v>
+      </c>
+      <c r="D158" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B159" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C158" s="3">
-        <v>1</v>
-      </c>
-      <c r="D158" s="3">
+      <c r="C159" s="3">
+        <v>1</v>
+      </c>
+      <c r="D159" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C159" s="3">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="B160" s="3" t="s">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
       </c>
       <c r="D160" s="3"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C161" s="3">
+        <v>1</v>
+      </c>
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C162" s="3">
+        <v>1</v>
+      </c>
+      <c r="D162" s="3"/>
+    </row>
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C163" s="3">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C164" s="3">
+        <v>1</v>
+      </c>
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C165" s="3">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C166" s="3">
+        <v>1</v>
+      </c>
+      <c r="D166" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C167" s="3">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3">
         <v>4</v>
       </c>
-      <c r="B161" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C161" s="3">
-        <v>1</v>
-      </c>
-      <c r="D161" s="3"/>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C162" s="3">
-        <v>1</v>
-      </c>
-      <c r="D162" s="3"/>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C163" s="3">
-        <v>1</v>
-      </c>
-      <c r="D163" s="3"/>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C164" s="3">
-        <v>1</v>
-      </c>
-      <c r="D164" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C165" s="3">
-        <v>1</v>
-      </c>
-      <c r="D165" s="3"/>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C166" s="3">
-        <v>1</v>
-      </c>
-      <c r="D166" s="3"/>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="C167" s="3">
-        <v>1</v>
-      </c>
-      <c r="D167" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>150</v>
+        <v>408</v>
       </c>
       <c r="C168" s="3">
         <v>1</v>
       </c>
-      <c r="D168" s="3">
-        <v>4</v>
-      </c>
+      <c r="D168" s="3"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C169" s="3">
         <v>1</v>
       </c>
-      <c r="D169" s="3"/>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D169" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="C170" s="3">
         <v>1</v>
       </c>
       <c r="D170" s="3"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>357</v>
+        <v>483</v>
       </c>
       <c r="C171" s="3">
         <v>1</v>
       </c>
       <c r="D171" s="3"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>483</v>
+        <v>159</v>
       </c>
       <c r="C172" s="3">
         <v>1</v>
       </c>
-      <c r="D172" s="3"/>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D172" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>159</v>
+        <v>323</v>
       </c>
       <c r="C173" s="3">
         <v>1</v>
       </c>
       <c r="D173" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="C174" s="3">
         <v>1</v>
       </c>
-      <c r="D174" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D174" s="3"/>
+    </row>
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>339</v>
+        <v>188</v>
       </c>
       <c r="C175" s="3">
         <v>1</v>
       </c>
-      <c r="D175" s="3"/>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D175" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C176" s="3">
         <v>1</v>
@@ -6149,268 +6158,268 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="C177" s="3">
+        <v>1</v>
+      </c>
+      <c r="D177" s="3"/>
+    </row>
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+      <c r="C178" s="3">
+        <v>1</v>
+      </c>
+      <c r="D178" s="3"/>
+    </row>
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3">
-        <v>2</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C179" s="3">
+        <v>1</v>
+      </c>
+      <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -6418,647 +6427,641 @@
         <v>49</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>436</v>
+        <v>212</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>329</v>
+        <v>182</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>278</v>
+        <v>436</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>30</v>
+        <v>431</v>
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>347</v>
+        <v>144</v>
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>281</v>
+        <v>352</v>
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>469</v>
+        <v>347</v>
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>348</v>
+        <v>281</v>
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>340</v>
+        <v>469</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>440</v>
+        <v>348</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>443</v>
+        <v>340</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>301</v>
+        <v>440</v>
       </c>
       <c r="C244" s="3"/>
       <c r="D244" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="C245" s="3"/>
       <c r="D245" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>245</v>
+        <v>383</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>461</v>
+        <v>303</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C249" s="3">
-        <v>1</v>
-      </c>
-      <c r="D249" s="3"/>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C251" s="3">
-        <v>1</v>
-      </c>
-      <c r="D251" s="3"/>
+        <v>416</v>
+      </c>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C252" s="3">
-        <v>1</v>
-      </c>
+      <c r="A252" s="3"/>
+      <c r="B252" s="3"/>
+      <c r="C252" s="3"/>
       <c r="D252" s="3"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -7085,16 +7088,15 @@
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257" s="3"/>
-      <c r="B257" s="3"/>
-      <c r="C257" s="3"/>
-      <c r="D257" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D252" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
-      <sortCondition descending="1" ref="C1:C248"/>
+  <autoFilter ref="A1:D251" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Galatasaray"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D251">
+      <sortCondition descending="1" ref="C1:C251"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7103,15 +7105,15 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5027319E-1F2C-4ACC-91C6-5F3CC481EF4D}">
           <x14:formula1>
-            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A193, BD!$A$1:$Q$1, 0))</xm:f>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A192, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B193:B257</xm:sqref>
+          <xm:sqref>B192:B256</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{615D4765-D08C-4B4D-8747-FBF8EC6F5D94}">
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A193:A257</xm:sqref>
+          <xm:sqref>A192:A256</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9064,7 +9066,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -9957,7 +9959,7 @@
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -10015,7 +10017,9 @@
       <c r="B78" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C78" s="3"/>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
       <c r="D78" s="3">
         <v>1</v>
       </c>
@@ -10077,7 +10081,7 @@
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -11329,7 +11333,7 @@
       <c r="D249" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D120" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:D122" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D97">
       <sortCondition descending="1" ref="C1:C96"/>
     </sortState>
